--- a/outs/todo/08_top_results_to_fill_in.xlsx
+++ b/outs/todo/08_top_results_to_fill_in.xlsx
@@ -12,13 +12,13 @@
     <sheet name="Tier 3 - Secretary or legis." sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tier 3 - Secretary or legis.'!$A$1:$S$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tier 3 - Secretary or legis.'!$A$1:$Y$7</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="353">
   <si>
     <t xml:space="preserve">How to fill this in</t>
   </si>
@@ -32,25 +32,28 @@
     <t xml:space="preserve">Deadline and award come straight from each opportunity's current record on Grants.gov (checked Sept 29-30, 2026). Forecast deadlines are Grants.gov's estimates. A blank award means Grants.gov states no ceiling.</t>
   </si>
   <si>
-    <t xml:space="preserve">Impact score (0-100) orders opportunities within a tier only; it never moves anything between tiers. It is the average of five parts, each 0-100, with equal weights:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Plan fit: the AI labeler's rating of fit with the agency's strategic plan (strong = 100, partial = 50, none = 0).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  People reached: how many North Carolinians are in the population the opportunity serves, ranked against the other opportunities in view.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Help per person: award ceiling divided by that population, ranked the same way.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Award size: the Grants.gov award ceiling, ranked the same way.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Program priorities: the writer's weight for the opportunity's program area, out of 3. The default weight is 1 for every area, which scores 33.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A blank part means the data isn't available (for example, no award ceiling), and the score is the average of the parts that are.</t>
+    <t xml:space="preserve">Impact score (0-100) orders opportunities within a tier only; it never moves anything between tiers. For each of five parts the sheet shows the actual number and the points it adds; the points add up to the score (small differences are rounding).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Plan fit: the AI labeler's rating of fit with the agency's strategic plan. Strong earns full points, partial half, none zero.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  People reached: how many North Carolinians are in the population the opportunity serves (the population is named in the next column).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Help per person: the award ceiling divided by that population.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Award size: the award ceiling on Grants.gov (shown in the Award ceiling column).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Program priorities: the writer's weight for the opportunity's program area, out of 3. The default is 1 for every area.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">People reached, help per person and award size earn points by how their number ranks against all the opportunities in the tool's view (about 400), not by the number alone. The biggest number gets full points; the median gets about half.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With the default equal weights, each part can add at most 100 / (number of parts with a number): 20 points when all five have one. A blank part has no number (for example, no award ceiling), and the others share its points.</t>
   </si>
   <si>
     <t xml:space="preserve">Grants.gov ID is the number in grants.gov listing addresses; Simpler.Grants.gov ID is the code in the link, which opens the listing.</t>
@@ -65,19 +68,37 @@
     <t xml:space="preserve">Impact score (0-100)</t>
   </si>
   <si>
-    <t xml:space="preserve">Plan fit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">People reached</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help per person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Award size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Program priorities</t>
+    <t xml:space="preserve">Plan fit: labeler's rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan fit: points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">People reached: NC people served</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Population served</t>
+  </si>
+  <si>
+    <t xml:space="preserve">People reached: points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help per person: award / people ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help per person: points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Award size: points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program priority weight (of 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program priorities: points</t>
   </si>
   <si>
     <t xml:space="preserve">Opportunity number</t>
@@ -116,6 +137,15 @@
     <t xml:space="preserve">DHHS</t>
   </si>
   <si>
+    <t xml:space="preserve">partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All NC residents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health access and workforce</t>
+  </si>
+  <si>
     <t xml:space="preserve">HRSA-27-007</t>
   </si>
   <si>
@@ -137,6 +167,12 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/c30fddfd-2094-4cf0-ba21-04b6736fc755</t>
   </si>
   <si>
+    <t xml:space="preserve">strong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public health preparedness, infectious disease and disaster</t>
+  </si>
+  <si>
     <t xml:space="preserve">CDC-RFA-PS-27-0009</t>
   </si>
   <si>
@@ -200,6 +236,9 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/6076b54f-ab56-4ed2-81f5-8b43c030a4c0</t>
   </si>
   <si>
+    <t xml:space="preserve">Behavioral health and crisis</t>
+  </si>
+  <si>
     <t xml:space="preserve">HRSA-27-070</t>
   </si>
   <si>
@@ -215,6 +254,9 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/be465a8b-8694-4eef-9801-5160a92c7cdf</t>
   </si>
   <si>
+    <t xml:space="preserve">Adults with frequent mental distress</t>
+  </si>
+  <si>
     <t xml:space="preserve">HRSA-27-077</t>
   </si>
   <si>
@@ -230,6 +272,12 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/1613e128-508f-47e1-9bf2-e2c02e7d79b1</t>
   </si>
   <si>
+    <t xml:space="preserve">Children under 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Child and family well-being</t>
+  </si>
+  <si>
     <t xml:space="preserve">HRSA-27-031</t>
   </si>
   <si>
@@ -263,6 +311,9 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/b3577f33-eee0-49fb-aeba-2ea0b02fe59e</t>
   </si>
   <si>
+    <t xml:space="preserve">Food and nutrition security</t>
+  </si>
+  <si>
     <t xml:space="preserve">HRSA-27-019</t>
   </si>
   <si>
@@ -293,6 +344,12 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/217a3975-7543-445d-9638-8026297a75c4</t>
   </si>
   <si>
+    <t xml:space="preserve">Women who gave birth in the past year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maternal, infant and reproductive health</t>
+  </si>
+  <si>
     <t xml:space="preserve">HRSA-27-047</t>
   </si>
   <si>
@@ -479,6 +536,9 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/8bb15754-c013-462d-b305-f2a8dd116e08</t>
   </si>
   <si>
+    <t xml:space="preserve">People with a substance use disorder</t>
+  </si>
+  <si>
     <t xml:space="preserve">CDC-RFA-PS-27-0239</t>
   </si>
   <si>
@@ -524,6 +584,9 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/18c0a9f1-fe39-4c7a-8ffd-1d8c656d666f</t>
   </si>
   <si>
+    <t xml:space="preserve">People without health insurance</t>
+  </si>
+  <si>
     <t xml:space="preserve">HRSA-27-063</t>
   </si>
   <si>
@@ -902,6 +965,9 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/06024144-a58a-42d8-8813-75357d9bb7fe</t>
   </si>
   <si>
+    <t xml:space="preserve">Veterans</t>
+  </si>
+  <si>
     <t xml:space="preserve">VA-GPD-FORECAST-FY2026-FY2028</t>
   </si>
   <si>
@@ -972,6 +1038,9 @@
   </si>
   <si>
     <t xml:space="preserve">DMVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aging, disability and long-term care</t>
   </si>
   <si>
     <t xml:space="preserve">VA-GRANTS-112508-002</t>
@@ -1014,9 +1083,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="11">
     <numFmt numFmtId="166" formatCode="mmm d, yyyy"/>
     <numFmt numFmtId="167" formatCode="$#,##0"/>
+    <numFmt numFmtId="168" formatCode="#,##0"/>
+    <numFmt numFmtId="169" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="#,##0"/>
+    <numFmt numFmtId="172" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="173" formatCode="0.0"/>
+    <numFmt numFmtId="174" formatCode="#,##0"/>
+    <numFmt numFmtId="175" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -1079,7 +1157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1094,11 +1172,38 @@
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="174" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="175" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1453,6 +1558,11 @@
         <v>11</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -1467,86 +1577,110 @@
     <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="7.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="9.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="7.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="8.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="8.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="7.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="22.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="11.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="20.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="48.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="16.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="11.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="13.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="14.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="13.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="55.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="30.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="22.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="12.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="8.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="10.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="22.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="9.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="9.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="22.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="11.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="20.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="48.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="11.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="13.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="14.71" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="13.71" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="55.71" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="30.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -1554,56 +1688,74 @@
       <c r="C2" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>34</v>
+      <c r="D2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="K2" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O2" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U2" s="4" t="n">
         <v>46386</v>
       </c>
-      <c r="P2" s="5" t="n">
+      <c r="V2" s="5" t="n">
         <v>22024900</v>
       </c>
-      <c r="Q2" s="5" t="n">
+      <c r="W2" s="5" t="n">
         <v>398400</v>
       </c>
-      <c r="R2" s="6"/>
-      <c r="S2" s="7" t="s">
-        <v>38</v>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -1611,48 +1763,64 @@
       <c r="C3" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>41</v>
-      </c>
+      <c r="H3" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
       <c r="L3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U3" s="4" t="n">
         <v>46434</v>
       </c>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="7" t="s">
-        <v>44</v>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="10" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -1660,56 +1828,74 @@
       <c r="C4" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K4" s="2" t="s">
+      <c r="M4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="T4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O4" s="4" t="n">
+      <c r="U4" s="4" t="n">
         <v>46391</v>
       </c>
-      <c r="P4" s="5" t="n">
+      <c r="V4" s="5" t="n">
         <v>22000000</v>
       </c>
-      <c r="Q4" s="5" t="n">
+      <c r="W4" s="5" t="n">
         <v>3500000</v>
       </c>
-      <c r="R4" s="6"/>
-      <c r="S4" s="7" t="s">
-        <v>50</v>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="10" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>4</v>
@@ -1717,56 +1903,74 @@
       <c r="C5" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E5" s="2" t="n">
+      <c r="D5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O5" s="4" t="n">
+      <c r="R5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U5" s="4" t="n">
         <v>46386</v>
       </c>
-      <c r="P5" s="5" t="n">
+      <c r="V5" s="5" t="n">
         <v>19182000</v>
       </c>
-      <c r="Q5" s="5" t="n">
+      <c r="W5" s="5" t="n">
         <v>1215700</v>
       </c>
-      <c r="R5" s="6"/>
-      <c r="S5" s="7" t="s">
-        <v>55</v>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="10" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>5</v>
@@ -1774,56 +1978,74 @@
       <c r="C6" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>58</v>
+      <c r="D6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O6" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U6" s="4" t="n">
         <v>46395</v>
       </c>
-      <c r="P6" s="5" t="n">
+      <c r="V6" s="5" t="n">
         <v>15335500</v>
       </c>
-      <c r="Q6" s="5" t="n">
+      <c r="W6" s="5" t="n">
         <v>567000</v>
       </c>
-      <c r="R6" s="6"/>
-      <c r="S6" s="7" t="s">
-        <v>59</v>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="10" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>6</v>
@@ -1831,54 +2053,72 @@
       <c r="C7" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>62</v>
+      <c r="D7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>18.5</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O7" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U7" s="4" t="n">
         <v>46461</v>
       </c>
-      <c r="P7" s="5" t="n">
+      <c r="V7" s="5" t="n">
         <v>9000000</v>
       </c>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="7" t="s">
-        <v>64</v>
+      <c r="W7" s="5"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="10" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
@@ -1886,54 +2126,72 @@
       <c r="C8" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="D8" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>67</v>
+      <c r="D8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1402172</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>18.6</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O8" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U8" s="4" t="n">
         <v>46328</v>
       </c>
-      <c r="P8" s="5" t="n">
+      <c r="V8" s="5" t="n">
         <v>10000000</v>
       </c>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="7" t="s">
-        <v>69</v>
+      <c r="W8" s="5"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="10" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>8</v>
@@ -1941,56 +2199,74 @@
       <c r="C9" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="D9" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F9" s="2" t="n">
+      <c r="D9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2322823</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="K9" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="R9" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O9" s="4" t="n">
+      <c r="S9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U9" s="4" t="n">
         <v>46407</v>
       </c>
-      <c r="P9" s="5" t="n">
+      <c r="V9" s="5" t="n">
         <v>5149000</v>
       </c>
-      <c r="Q9" s="5" t="n">
+      <c r="W9" s="5" t="n">
         <v>5149000</v>
       </c>
-      <c r="R9" s="6"/>
-      <c r="S9" s="7" t="s">
-        <v>74</v>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="10" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
@@ -1998,56 +2274,74 @@
       <c r="C10" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O10" s="4" t="n">
+      <c r="M10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U10" s="4" t="n">
         <v>46387</v>
       </c>
-      <c r="P10" s="5" t="n">
+      <c r="V10" s="5" t="n">
         <v>1140000</v>
       </c>
-      <c r="Q10" s="5" t="n">
+      <c r="W10" s="5" t="n">
         <v>850000</v>
       </c>
-      <c r="R10" s="6"/>
-      <c r="S10" s="7" t="s">
-        <v>80</v>
+      <c r="X10" s="9"/>
+      <c r="Y10" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>10</v>
@@ -2055,56 +2349,74 @@
       <c r="C11" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>83</v>
+      <c r="D11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>13.8</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O11" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U11" s="4" t="n">
         <v>46357</v>
       </c>
-      <c r="P11" s="5" t="n">
+      <c r="V11" s="5" t="n">
         <v>1000000</v>
       </c>
-      <c r="Q11" s="5" t="n">
+      <c r="W11" s="5" t="n">
         <v>1000000</v>
       </c>
-      <c r="R11" s="6"/>
-      <c r="S11" s="7" t="s">
-        <v>85</v>
+      <c r="X11" s="9"/>
+      <c r="Y11" s="10" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>11</v>
@@ -2112,56 +2424,74 @@
       <c r="C12" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O12" s="4" t="n">
+      <c r="M12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U12" s="4" t="n">
         <v>46438</v>
       </c>
-      <c r="P12" s="5" t="n">
+      <c r="V12" s="5" t="n">
         <v>1000000</v>
       </c>
-      <c r="Q12" s="5" t="n">
+      <c r="W12" s="5" t="n">
         <v>350000</v>
       </c>
-      <c r="R12" s="6"/>
-      <c r="S12" s="7" t="s">
-        <v>90</v>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="10" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>12</v>
@@ -2169,54 +2499,72 @@
       <c r="C13" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>93</v>
+      <c r="D13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>127227</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>13.8</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O13" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U13" s="4" t="n">
         <v>46497</v>
       </c>
-      <c r="P13" s="5" t="n">
+      <c r="V13" s="5" t="n">
         <v>1000000</v>
       </c>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="7" t="s">
-        <v>95</v>
+      <c r="W13" s="5"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="10" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>13</v>
@@ -2224,48 +2572,64 @@
       <c r="C14" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I14" s="7"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O14" s="4" t="n">
+      <c r="M14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U14" s="4" t="n">
         <v>46398</v>
       </c>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="7" t="s">
-        <v>100</v>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="9"/>
+      <c r="Y14" s="10" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>14</v>
@@ -2273,54 +2637,72 @@
       <c r="C15" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="D15" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>103</v>
+      <c r="D15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O15" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U15" s="4" t="n">
         <v>46464</v>
       </c>
-      <c r="P15" s="5" t="n">
+      <c r="V15" s="5" t="n">
         <v>750000</v>
       </c>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="7" t="s">
-        <v>105</v>
+      <c r="W15" s="5"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="10" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
@@ -2328,48 +2710,64 @@
       <c r="C16" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I16" s="7"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O16" s="4" t="n">
+      <c r="M16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U16" s="4" t="n">
         <v>46477</v>
       </c>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="7" t="s">
-        <v>111</v>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="9"/>
+      <c r="Y16" s="10" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>16</v>
@@ -2377,48 +2775,64 @@
       <c r="C17" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="D17" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>114</v>
-      </c>
+      <c r="D17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I17" s="7"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
       <c r="L17" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O17" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U17" s="4" t="n">
         <v>46503</v>
       </c>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="7" t="s">
-        <v>116</v>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="10" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>17</v>
@@ -2426,48 +2840,64 @@
       <c r="C18" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I18" s="7"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O18" s="4" t="n">
+      <c r="M18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U18" s="4" t="n">
         <v>46538</v>
       </c>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="7" t="s">
-        <v>121</v>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="9"/>
+      <c r="Y18" s="10" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>18</v>
@@ -2475,46 +2905,62 @@
       <c r="C19" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="D19" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>124</v>
-      </c>
+      <c r="D19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I19" s="7"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
       <c r="L19" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O19" s="4"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="6"/>
-      <c r="S19" s="7" t="s">
-        <v>127</v>
+        <v>97</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U19" s="4"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="9"/>
+      <c r="Y19" s="10" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>19</v>
@@ -2522,56 +2968,74 @@
       <c r="C20" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K20" s="8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L20" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O20" s="4" t="n">
+      <c r="M20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U20" s="4" t="n">
         <v>46468</v>
       </c>
-      <c r="P20" s="5" t="n">
+      <c r="V20" s="5" t="n">
         <v>725000</v>
       </c>
-      <c r="Q20" s="5" t="n">
+      <c r="W20" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="R20" s="6"/>
-      <c r="S20" s="7" t="s">
-        <v>132</v>
+      <c r="X20" s="9"/>
+      <c r="Y20" s="10" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>20</v>
@@ -2579,54 +3043,72 @@
       <c r="C21" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="L21" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O21" s="4" t="n">
+      <c r="M21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U21" s="4" t="n">
         <v>46405</v>
       </c>
-      <c r="P21" s="5" t="n">
+      <c r="V21" s="5" t="n">
         <v>700000</v>
       </c>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="6"/>
-      <c r="S21" s="7" t="s">
-        <v>137</v>
+      <c r="W21" s="5"/>
+      <c r="X21" s="9"/>
+      <c r="Y21" s="10" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>21</v>
@@ -2634,56 +3116,74 @@
       <c r="C22" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K22" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O22" s="4" t="n">
+      <c r="M22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U22" s="4" t="n">
         <v>46386</v>
       </c>
-      <c r="P22" s="5" t="n">
+      <c r="V22" s="5" t="n">
         <v>685000</v>
       </c>
-      <c r="Q22" s="5" t="n">
+      <c r="W22" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="R22" s="6"/>
-      <c r="S22" s="7" t="s">
-        <v>142</v>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="10" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>22</v>
@@ -2691,54 +3191,72 @@
       <c r="C23" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K23" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="L23" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O23" s="4" t="n">
+      <c r="M23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U23" s="4" t="n">
         <v>46466</v>
       </c>
-      <c r="P23" s="5" t="n">
+      <c r="V23" s="5" t="n">
         <v>650000</v>
       </c>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="6"/>
-      <c r="S23" s="7" t="s">
-        <v>147</v>
+      <c r="W23" s="5"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="10" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>23</v>
@@ -2746,56 +3264,74 @@
       <c r="C24" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D24" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>150</v>
+      <c r="D24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K24" s="8" t="n">
+        <v>8.9</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O24" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U24" s="4" t="n">
         <v>46462</v>
       </c>
-      <c r="P24" s="5" t="n">
+      <c r="V24" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="Q24" s="5" t="n">
+      <c r="W24" s="5" t="n">
         <v>300000</v>
       </c>
-      <c r="R24" s="6"/>
-      <c r="S24" s="7" t="s">
-        <v>152</v>
+      <c r="X24" s="9"/>
+      <c r="Y24" s="10" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>24</v>
@@ -2803,46 +3339,60 @@
       <c r="C25" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="F25" s="6"/>
+      <c r="G25" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H25" s="8"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O25" s="4" t="n">
+      <c r="M25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U25" s="4" t="n">
         <v>46531</v>
       </c>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="6"/>
-      <c r="S25" s="7" t="s">
-        <v>157</v>
+      <c r="V25" s="5"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="10" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>25</v>
@@ -2850,56 +3400,74 @@
       <c r="C26" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K26" s="8" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L26" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O26" s="4" t="n">
+      <c r="M26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U26" s="4" t="n">
         <v>46532</v>
       </c>
-      <c r="P26" s="5" t="n">
+      <c r="V26" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="Q26" s="5" t="n">
+      <c r="W26" s="5" t="n">
         <v>250000</v>
       </c>
-      <c r="R26" s="6"/>
-      <c r="S26" s="7" t="s">
-        <v>162</v>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="10" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>26</v>
@@ -2907,54 +3475,72 @@
       <c r="C27" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D27" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>165</v>
+      <c r="D27" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>5.2</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O27" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U27" s="4" t="n">
         <v>46508</v>
       </c>
-      <c r="P27" s="5" t="n">
+      <c r="V27" s="5" t="n">
         <v>300000</v>
       </c>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="6"/>
-      <c r="S27" s="7" t="s">
-        <v>167</v>
+      <c r="W27" s="5"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="10" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>27</v>
@@ -2962,75 +3548,91 @@
       <c r="C28" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>1073923</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I28" s="7"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O28" s="4" t="n">
+      <c r="M28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T28" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U28" s="4" t="n">
         <v>46387</v>
       </c>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="7" t="s">
-        <v>172</v>
+      <c r="V28" s="5"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="10" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S28"/>
+  <autoFilter ref="A1:Y28"/>
   <hyperlinks>
-    <hyperlink ref="S2" r:id="rId1h"/>
-    <hyperlink ref="S3" r:id="rId2h"/>
-    <hyperlink ref="S4" r:id="rId3h"/>
-    <hyperlink ref="S5" r:id="rId4h"/>
-    <hyperlink ref="S6" r:id="rId5h"/>
-    <hyperlink ref="S7" r:id="rId6h"/>
-    <hyperlink ref="S8" r:id="rId7h"/>
-    <hyperlink ref="S9" r:id="rId8h"/>
-    <hyperlink ref="S10" r:id="rId9h"/>
-    <hyperlink ref="S11" r:id="rId10h"/>
-    <hyperlink ref="S12" r:id="rId11h"/>
-    <hyperlink ref="S13" r:id="rId12h"/>
-    <hyperlink ref="S14" r:id="rId13h"/>
-    <hyperlink ref="S15" r:id="rId14h"/>
-    <hyperlink ref="S16" r:id="rId15h"/>
-    <hyperlink ref="S17" r:id="rId16h"/>
-    <hyperlink ref="S18" r:id="rId17h"/>
-    <hyperlink ref="S19" r:id="rId18h"/>
-    <hyperlink ref="S20" r:id="rId19h"/>
-    <hyperlink ref="S21" r:id="rId20h"/>
-    <hyperlink ref="S22" r:id="rId21h"/>
-    <hyperlink ref="S23" r:id="rId22h"/>
-    <hyperlink ref="S24" r:id="rId23h"/>
-    <hyperlink ref="S25" r:id="rId24h"/>
-    <hyperlink ref="S26" r:id="rId25h"/>
-    <hyperlink ref="S27" r:id="rId26h"/>
-    <hyperlink ref="S28" r:id="rId27h"/>
+    <hyperlink ref="Y2" r:id="rId1h"/>
+    <hyperlink ref="Y3" r:id="rId2h"/>
+    <hyperlink ref="Y4" r:id="rId3h"/>
+    <hyperlink ref="Y5" r:id="rId4h"/>
+    <hyperlink ref="Y6" r:id="rId5h"/>
+    <hyperlink ref="Y7" r:id="rId6h"/>
+    <hyperlink ref="Y8" r:id="rId7h"/>
+    <hyperlink ref="Y9" r:id="rId8h"/>
+    <hyperlink ref="Y10" r:id="rId9h"/>
+    <hyperlink ref="Y11" r:id="rId10h"/>
+    <hyperlink ref="Y12" r:id="rId11h"/>
+    <hyperlink ref="Y13" r:id="rId12h"/>
+    <hyperlink ref="Y14" r:id="rId13h"/>
+    <hyperlink ref="Y15" r:id="rId14h"/>
+    <hyperlink ref="Y16" r:id="rId15h"/>
+    <hyperlink ref="Y17" r:id="rId16h"/>
+    <hyperlink ref="Y18" r:id="rId17h"/>
+    <hyperlink ref="Y19" r:id="rId18h"/>
+    <hyperlink ref="Y20" r:id="rId19h"/>
+    <hyperlink ref="Y21" r:id="rId20h"/>
+    <hyperlink ref="Y22" r:id="rId21h"/>
+    <hyperlink ref="Y23" r:id="rId22h"/>
+    <hyperlink ref="Y24" r:id="rId23h"/>
+    <hyperlink ref="Y25" r:id="rId24h"/>
+    <hyperlink ref="Y26" r:id="rId25h"/>
+    <hyperlink ref="Y27" r:id="rId26h"/>
+    <hyperlink ref="Y28" r:id="rId27h"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3045,86 +3647,110 @@
     <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="7.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="9.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="7.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="8.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="8.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="7.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="22.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="11.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="20.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="48.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="16.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="11.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="13.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="14.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="13.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="55.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="30.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="22.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="12.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="8.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="10.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="22.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="9.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="9.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="22.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="11.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="20.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="48.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="11.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="13.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="14.71" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="13.71" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="55.71" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="30.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -3132,56 +3758,74 @@
       <c r="C2" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>175</v>
+      <c r="D2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I2" s="12" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J2" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="K2" s="13" t="n">
+        <v>17.3</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="O2" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="U2" s="4" t="n">
         <v>46429</v>
       </c>
-      <c r="P2" s="5" t="n">
+      <c r="V2" s="5" t="n">
         <v>5000000</v>
       </c>
-      <c r="Q2" s="5" t="n">
+      <c r="W2" s="5" t="n">
         <v>50000</v>
       </c>
-      <c r="R2" s="6"/>
-      <c r="S2" s="7" t="s">
-        <v>179</v>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="10" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -3189,48 +3833,64 @@
       <c r="C3" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>182</v>
-      </c>
+      <c r="D3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="13" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I3" s="12"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
       <c r="L3" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U3" s="4" t="n">
         <v>46507</v>
       </c>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="7" t="s">
-        <v>185</v>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="10" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -3238,56 +3898,74 @@
       <c r="C4" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>188</v>
+      <c r="D4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>2322823</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I4" s="12" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>20</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="O4" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="U4" s="4" t="n">
         <v>46661</v>
       </c>
-      <c r="P4" s="5" t="n">
+      <c r="V4" s="5" t="n">
         <v>100000000</v>
       </c>
-      <c r="Q4" s="5" t="n">
+      <c r="W4" s="5" t="n">
         <v>1000000</v>
       </c>
-      <c r="R4" s="6"/>
-      <c r="S4" s="7" t="s">
-        <v>191</v>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="10" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>4</v>
@@ -3295,56 +3973,74 @@
       <c r="C5" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="O5" s="4" t="n">
+      <c r="M5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="U5" s="4" t="n">
         <v>46331</v>
       </c>
-      <c r="P5" s="5" t="n">
+      <c r="V5" s="5" t="n">
         <v>6000000</v>
       </c>
-      <c r="Q5" s="5" t="n">
+      <c r="W5" s="5" t="n">
         <v>1750000</v>
       </c>
-      <c r="R5" s="6"/>
-      <c r="S5" s="7" t="s">
-        <v>196</v>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="10" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>5</v>
@@ -3352,56 +4048,74 @@
       <c r="C6" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="K6" s="13" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="K6" s="2" t="s">
+      <c r="M6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="T6" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="O6" s="4" t="n">
+      <c r="U6" s="4" t="n">
         <v>46357</v>
       </c>
-      <c r="P6" s="5" t="n">
+      <c r="V6" s="5" t="n">
         <v>5750000</v>
       </c>
-      <c r="Q6" s="5" t="n">
+      <c r="W6" s="5" t="n">
         <v>3000000</v>
       </c>
-      <c r="R6" s="6"/>
-      <c r="S6" s="7" t="s">
-        <v>201</v>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="10" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>6</v>
@@ -3409,50 +4123,64 @@
       <c r="C7" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>204</v>
+      <c r="D7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F7" s="11"/>
+      <c r="G7" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H7" s="13"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13" t="n">
+        <v>14.9</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O7" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U7" s="4" t="n">
         <v>46483</v>
       </c>
-      <c r="P7" s="5" t="n">
+      <c r="V7" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="7" t="s">
-        <v>206</v>
+      <c r="W7" s="5"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="10" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
@@ -3460,56 +4188,74 @@
       <c r="C8" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="D8" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>209</v>
+      <c r="D8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>17</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O8" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U8" s="4" t="n">
         <v>46412</v>
       </c>
-      <c r="P8" s="5" t="n">
+      <c r="V8" s="5" t="n">
         <v>4900000</v>
       </c>
-      <c r="Q8" s="5" t="n">
+      <c r="W8" s="5" t="n">
         <v>790000</v>
       </c>
-      <c r="R8" s="6"/>
-      <c r="S8" s="7" t="s">
-        <v>211</v>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="10" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>8</v>
@@ -3517,56 +4263,74 @@
       <c r="C9" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="D9" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>214</v>
+      <c r="D9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>1402172</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>14.8</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O9" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U9" s="4" t="n">
         <v>46494</v>
       </c>
-      <c r="P9" s="5" t="n">
+      <c r="V9" s="5" t="n">
         <v>1200000</v>
       </c>
-      <c r="Q9" s="5" t="n">
+      <c r="W9" s="5" t="n">
         <v>650000</v>
       </c>
-      <c r="R9" s="6"/>
-      <c r="S9" s="7" t="s">
-        <v>217</v>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="10" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
@@ -3574,56 +4338,74 @@
       <c r="C10" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>220</v>
+      <c r="D10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>2322823</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>18.1</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O10" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U10" s="4" t="n">
         <v>46498</v>
       </c>
-      <c r="P10" s="5" t="n">
+      <c r="V10" s="5" t="n">
         <v>6750000</v>
       </c>
-      <c r="Q10" s="5" t="n">
+      <c r="W10" s="5" t="n">
         <v>6750000</v>
       </c>
-      <c r="R10" s="6"/>
-      <c r="S10" s="7" t="s">
-        <v>222</v>
+      <c r="X10" s="9"/>
+      <c r="Y10" s="10" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>10</v>
@@ -3631,52 +4413,66 @@
       <c r="C11" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>225</v>
+      <c r="D11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H11" s="13"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13" t="n">
+        <v>28.8</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O11" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U11" s="4" t="n">
         <v>46469</v>
       </c>
-      <c r="P11" s="5" t="n">
+      <c r="V11" s="5" t="n">
         <v>5000000</v>
       </c>
-      <c r="Q11" s="5" t="n">
+      <c r="W11" s="5" t="n">
         <v>5000000</v>
       </c>
-      <c r="R11" s="6"/>
-      <c r="S11" s="7" t="s">
-        <v>227</v>
+      <c r="X11" s="9"/>
+      <c r="Y11" s="10" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>11</v>
@@ -3684,56 +4480,74 @@
       <c r="C12" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="D12" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>230</v>
+      <c r="D12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>2322823</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>17.3</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O12" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U12" s="4" t="n">
         <v>46441</v>
       </c>
-      <c r="P12" s="5" t="n">
+      <c r="V12" s="5" t="n">
         <v>5000000</v>
       </c>
-      <c r="Q12" s="5" t="n">
+      <c r="W12" s="5" t="n">
         <v>5000000</v>
       </c>
-      <c r="R12" s="6"/>
-      <c r="S12" s="7" t="s">
-        <v>232</v>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="10" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>12</v>
@@ -3741,56 +4555,74 @@
       <c r="C13" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>9.3</v>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F13" s="2" t="n">
+      <c r="M13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="T13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O13" s="4" t="n">
+      <c r="U13" s="4" t="n">
         <v>46444</v>
       </c>
-      <c r="P13" s="5" t="n">
+      <c r="V13" s="5" t="n">
         <v>1400000</v>
       </c>
-      <c r="Q13" s="5" t="n">
+      <c r="W13" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="R13" s="6"/>
-      <c r="S13" s="7" t="s">
-        <v>237</v>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="10" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>13</v>
@@ -3798,56 +4630,74 @@
       <c r="C14" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="D14" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>240</v>
+      <c r="D14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>2322823</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>11.9</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O14" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U14" s="4" t="n">
         <v>46498</v>
       </c>
-      <c r="P14" s="5" t="n">
+      <c r="V14" s="5" t="n">
         <v>700000</v>
       </c>
-      <c r="Q14" s="5" t="n">
+      <c r="W14" s="5" t="n">
         <v>700000</v>
       </c>
-      <c r="R14" s="6"/>
-      <c r="S14" s="7" t="s">
-        <v>242</v>
+      <c r="X14" s="9"/>
+      <c r="Y14" s="10" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>14</v>
@@ -3855,56 +4705,74 @@
       <c r="C15" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="O15" s="4" t="n">
+      <c r="M15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="U15" s="4" t="n">
         <v>46331</v>
       </c>
-      <c r="P15" s="5" t="n">
+      <c r="V15" s="5" t="n">
         <v>1000000</v>
       </c>
-      <c r="Q15" s="5" t="n">
+      <c r="W15" s="5" t="n">
         <v>750000</v>
       </c>
-      <c r="R15" s="6"/>
-      <c r="S15" s="7" t="s">
-        <v>247</v>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="10" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
@@ -3912,56 +4780,74 @@
       <c r="C16" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="D16" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>250</v>
+      <c r="D16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>13.3</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O16" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U16" s="4" t="n">
         <v>46455</v>
       </c>
-      <c r="P16" s="5" t="n">
+      <c r="V16" s="5" t="n">
         <v>900000</v>
       </c>
-      <c r="Q16" s="5" t="n">
+      <c r="W16" s="5" t="n">
         <v>450000</v>
       </c>
-      <c r="R16" s="6"/>
-      <c r="S16" s="7" t="s">
-        <v>252</v>
+      <c r="X16" s="9"/>
+      <c r="Y16" s="10" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>16</v>
@@ -3969,48 +4855,64 @@
       <c r="C17" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I17" s="12"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O17" s="4" t="n">
+      <c r="M17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U17" s="4" t="n">
         <v>46454</v>
       </c>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="7" t="s">
-        <v>257</v>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="10" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>17</v>
@@ -4018,48 +4920,64 @@
       <c r="C18" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I18" s="12"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O18" s="4" t="n">
+      <c r="M18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U18" s="4" t="n">
         <v>46469</v>
       </c>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="7" t="s">
-        <v>262</v>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="9"/>
+      <c r="Y18" s="10" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>18</v>
@@ -4067,48 +4985,64 @@
       <c r="C19" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I19" s="12"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O19" s="4" t="n">
+      <c r="M19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U19" s="4" t="n">
         <v>46539</v>
       </c>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="6"/>
-      <c r="S19" s="7" t="s">
-        <v>267</v>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="9"/>
+      <c r="Y19" s="10" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>19</v>
@@ -4116,48 +5050,64 @@
       <c r="C20" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I20" s="12"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="O20" s="4" t="n">
+      <c r="M20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="U20" s="4" t="n">
         <v>46783</v>
       </c>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="7" t="s">
-        <v>273</v>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="9"/>
+      <c r="Y20" s="10" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>20</v>
@@ -4165,48 +5115,64 @@
       <c r="C21" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D21" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>276</v>
-      </c>
+      <c r="D21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>127227</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I21" s="12"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
       <c r="L21" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O21" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U21" s="4" t="n">
         <v>46510</v>
       </c>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="6"/>
-      <c r="S21" s="7" t="s">
-        <v>278</v>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="9"/>
+      <c r="Y21" s="10" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>21</v>
@@ -4214,56 +5180,74 @@
       <c r="C22" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="D22" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>281</v>
+      <c r="D22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>10.6</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="O22" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="U22" s="4" t="n">
         <v>47052</v>
       </c>
-      <c r="P22" s="5" t="n">
+      <c r="V22" s="5" t="n">
         <v>550000</v>
       </c>
-      <c r="Q22" s="5" t="n">
+      <c r="W22" s="5" t="n">
         <v>50000</v>
       </c>
-      <c r="R22" s="6"/>
-      <c r="S22" s="7" t="s">
-        <v>283</v>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="10" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>22</v>
@@ -4271,56 +5255,74 @@
       <c r="C23" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L23" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O23" s="4" t="n">
+      <c r="M23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U23" s="4" t="n">
         <v>46510</v>
       </c>
-      <c r="P23" s="5" t="n">
+      <c r="V23" s="5" t="n">
         <v>450000</v>
       </c>
-      <c r="Q23" s="5" t="n">
+      <c r="W23" s="5" t="n">
         <v>450000</v>
       </c>
-      <c r="R23" s="6"/>
-      <c r="S23" s="7" t="s">
-        <v>288</v>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="10" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>23</v>
@@ -4328,48 +5330,64 @@
       <c r="C24" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D24" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>291</v>
-      </c>
+      <c r="D24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>1402172</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I24" s="12"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
       <c r="L24" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O24" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U24" s="4" t="n">
         <v>46461</v>
       </c>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="7" t="s">
-        <v>293</v>
+      <c r="V24" s="5"/>
+      <c r="W24" s="5"/>
+      <c r="X24" s="9"/>
+      <c r="Y24" s="10" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>24</v>
@@ -4377,70 +5395,86 @@
       <c r="C25" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D25" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>296</v>
-      </c>
+      <c r="D25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>618846</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I25" s="12"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
       <c r="L25" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O25" s="4"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="6"/>
-      <c r="S25" s="7" t="s">
-        <v>299</v>
+        <v>72</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U25" s="4"/>
+      <c r="V25" s="5"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="10" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S25"/>
+  <autoFilter ref="A1:Y25"/>
   <hyperlinks>
-    <hyperlink ref="S2" r:id="rId1h"/>
-    <hyperlink ref="S3" r:id="rId2h"/>
-    <hyperlink ref="S4" r:id="rId3h"/>
-    <hyperlink ref="S5" r:id="rId4h"/>
-    <hyperlink ref="S6" r:id="rId5h"/>
-    <hyperlink ref="S7" r:id="rId6h"/>
-    <hyperlink ref="S8" r:id="rId7h"/>
-    <hyperlink ref="S9" r:id="rId8h"/>
-    <hyperlink ref="S10" r:id="rId9h"/>
-    <hyperlink ref="S11" r:id="rId10h"/>
-    <hyperlink ref="S12" r:id="rId11h"/>
-    <hyperlink ref="S13" r:id="rId12h"/>
-    <hyperlink ref="S14" r:id="rId13h"/>
-    <hyperlink ref="S15" r:id="rId14h"/>
-    <hyperlink ref="S16" r:id="rId15h"/>
-    <hyperlink ref="S17" r:id="rId16h"/>
-    <hyperlink ref="S18" r:id="rId17h"/>
-    <hyperlink ref="S19" r:id="rId18h"/>
-    <hyperlink ref="S20" r:id="rId19h"/>
-    <hyperlink ref="S21" r:id="rId20h"/>
-    <hyperlink ref="S22" r:id="rId21h"/>
-    <hyperlink ref="S23" r:id="rId22h"/>
-    <hyperlink ref="S24" r:id="rId23h"/>
-    <hyperlink ref="S25" r:id="rId24h"/>
+    <hyperlink ref="Y2" r:id="rId1h"/>
+    <hyperlink ref="Y3" r:id="rId2h"/>
+    <hyperlink ref="Y4" r:id="rId3h"/>
+    <hyperlink ref="Y5" r:id="rId4h"/>
+    <hyperlink ref="Y6" r:id="rId5h"/>
+    <hyperlink ref="Y7" r:id="rId6h"/>
+    <hyperlink ref="Y8" r:id="rId7h"/>
+    <hyperlink ref="Y9" r:id="rId8h"/>
+    <hyperlink ref="Y10" r:id="rId9h"/>
+    <hyperlink ref="Y11" r:id="rId10h"/>
+    <hyperlink ref="Y12" r:id="rId11h"/>
+    <hyperlink ref="Y13" r:id="rId12h"/>
+    <hyperlink ref="Y14" r:id="rId13h"/>
+    <hyperlink ref="Y15" r:id="rId14h"/>
+    <hyperlink ref="Y16" r:id="rId15h"/>
+    <hyperlink ref="Y17" r:id="rId16h"/>
+    <hyperlink ref="Y18" r:id="rId17h"/>
+    <hyperlink ref="Y19" r:id="rId18h"/>
+    <hyperlink ref="Y20" r:id="rId19h"/>
+    <hyperlink ref="Y21" r:id="rId20h"/>
+    <hyperlink ref="Y22" r:id="rId21h"/>
+    <hyperlink ref="Y23" r:id="rId22h"/>
+    <hyperlink ref="Y24" r:id="rId23h"/>
+    <hyperlink ref="Y25" r:id="rId24h"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -4455,86 +5489,110 @@
     <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="7.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="9.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="7.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="8.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="8.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="7.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="22.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="11.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="20.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="48.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="16.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="11.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="13.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="14.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="13.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="55.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="30.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="22.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="12.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="8.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="10.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="22.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="9.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="9.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="22.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="11.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="20.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="48.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="11.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="13.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="14.71" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="13.71" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="55.71" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="30.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -4542,56 +5600,74 @@
       <c r="C2" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>302</v>
+      <c r="D2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" s="14" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="I2" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J2" s="16" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="K2" s="16" t="n">
+        <v>19</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O2" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="16" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U2" s="4" t="n">
         <v>46346</v>
       </c>
-      <c r="P2" s="5" t="n">
+      <c r="V2" s="5" t="n">
         <v>15000000</v>
       </c>
-      <c r="Q2" s="5" t="n">
+      <c r="W2" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="R2" s="6"/>
-      <c r="S2" s="7" t="s">
-        <v>305</v>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="10" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -4599,56 +5675,74 @@
       <c r="C3" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>308</v>
+      <c r="D3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>127227</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H3" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I3" s="15" t="n">
+        <v>381.97</v>
+      </c>
+      <c r="J3" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="K3" s="16" t="n">
+        <v>19.9</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="16" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U3" s="4" t="n">
         <v>46464</v>
       </c>
-      <c r="P3" s="5" t="n">
+      <c r="V3" s="5" t="n">
         <v>48596938</v>
       </c>
-      <c r="Q3" s="5" t="n">
+      <c r="W3" s="5" t="n">
         <v>3285203</v>
       </c>
-      <c r="R3" s="6"/>
-      <c r="S3" s="7" t="s">
-        <v>310</v>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="10" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -4656,56 +5750,74 @@
       <c r="C4" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>313</v>
+      <c r="D4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>10584340</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J4" s="16" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>19.4</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="O4" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="16" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="U4" s="4" t="n">
         <v>46398</v>
       </c>
-      <c r="P4" s="5" t="n">
+      <c r="V4" s="5" t="n">
         <v>22000000</v>
       </c>
-      <c r="Q4" s="5" t="n">
+      <c r="W4" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="R4" s="6"/>
-      <c r="S4" s="7" t="s">
-        <v>316</v>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="10" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -4713,54 +5825,72 @@
       <c r="C5" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>320</v>
+      <c r="D5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>618846</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>444.38</v>
+      </c>
+      <c r="J5" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="K5" s="16" t="n">
+        <v>20</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="O5" s="4"/>
-      <c r="P5" s="5" t="n">
+        <v>340</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="16" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="U5" s="4"/>
+      <c r="V5" s="5" t="n">
         <v>275000000</v>
       </c>
-      <c r="Q5" s="5" t="n">
+      <c r="W5" s="5" t="n">
         <v>260000</v>
       </c>
-      <c r="R5" s="6"/>
-      <c r="S5" s="7" t="s">
-        <v>323</v>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="10" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
@@ -4768,46 +5898,62 @@
       <c r="C6" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>296</v>
-      </c>
+      <c r="D6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>618846</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I6" s="15"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
       <c r="L6" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O6" s="4"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="7" t="s">
-        <v>299</v>
+        <v>72</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U6" s="4"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="10" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>3</v>
@@ -4815,62 +5961,80 @@
       <c r="C7" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F7" s="2" t="n">
+      <c r="D7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>618846</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J7" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="K7" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>326</v>
-      </c>
       <c r="L7" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O7" s="4" t="n">
+        <v>340</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="16" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U7" s="4" t="n">
         <v>46486</v>
       </c>
-      <c r="P7" s="5" t="n">
+      <c r="V7" s="5" t="n">
         <v>400000</v>
       </c>
-      <c r="Q7" s="5" t="n">
+      <c r="W7" s="5" t="n">
         <v>50000</v>
       </c>
-      <c r="R7" s="6"/>
-      <c r="S7" s="7" t="s">
-        <v>329</v>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="10" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S7"/>
+  <autoFilter ref="A1:Y7"/>
   <hyperlinks>
-    <hyperlink ref="S2" r:id="rId1h"/>
-    <hyperlink ref="S3" r:id="rId2h"/>
-    <hyperlink ref="S4" r:id="rId3h"/>
-    <hyperlink ref="S5" r:id="rId4h"/>
-    <hyperlink ref="S6" r:id="rId5h"/>
-    <hyperlink ref="S7" r:id="rId6h"/>
+    <hyperlink ref="Y2" r:id="rId1h"/>
+    <hyperlink ref="Y3" r:id="rId2h"/>
+    <hyperlink ref="Y4" r:id="rId3h"/>
+    <hyperlink ref="Y5" r:id="rId4h"/>
+    <hyperlink ref="Y6" r:id="rId5h"/>
+    <hyperlink ref="Y7" r:id="rId6h"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/outs/todo/08_top_results_to_fill_in.xlsx
+++ b/outs/todo/08_top_results_to_fill_in.xlsx
@@ -12,13 +12,13 @@
     <sheet name="Tier 3 - Secretary or legis." sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tier 3 - Secretary or legis.'!$A$1:$Y$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tier 3 - Secretary or legis.'!$A$1:$Z$7</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="357">
   <si>
     <t xml:space="preserve">How to fill this in</t>
   </si>
@@ -29,7 +29,7 @@
     <t xml:space="preserve">Write one line in the yellow Rationale column. Tie it to our five criteria: (1) we can be the applicant, (2) we have the capabilities or know the partner, (3) there is enough runway, (4) the award is worth the staff weeks, (5) the match is survivable at the writer's level.</t>
   </si>
   <si>
-    <t xml:space="preserve">Deadline and award come straight from each opportunity's current record on Grants.gov (checked Sept 29-30, 2026). Forecast deadlines are Grants.gov's estimates. A blank award means Grants.gov states no ceiling.</t>
+    <t xml:space="preserve">Deadline and award come from each opportunity's current record on Grants.gov (checked Sept 29-30, 2026). Forecast deadlines are Grants.gov's estimates. The award is Grants.gov's stated award ceiling; where it states none, the award is estimated as total program funding divided by the expected number of awards, and the Award source column says so. A blank award means Grants.gov gives neither.</t>
   </si>
   <si>
     <t xml:space="preserve">Impact score (0-100) orders opportunities within a tier only; it never moves anything between tiers. For each of five parts the sheet shows the actual number and the points it adds; the points add up to the score (small differences are rounding).</t>
@@ -41,10 +41,10 @@
     <t xml:space="preserve">  People reached: how many North Carolinians are in the population the opportunity serves (the population is named in the next column).</t>
   </si>
   <si>
-    <t xml:space="preserve">  Help per person: the award ceiling divided by that population.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Award size: the award ceiling on Grants.gov (shown in the Award ceiling column).</t>
+    <t xml:space="preserve">  Help per person: the award per recipient divided by that population.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Award size: the award per recipient (shown in the Award per recipient column, with its source).</t>
   </si>
   <si>
     <t xml:space="preserve">  Program priorities: the writer's weight for the opportunity's program area, out of 3. The default is 1 for every area.</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">People reached, help per person and award size earn points by how their number ranks against all the opportunities in the tool's view (about 400), not by the number alone. The biggest number gets full points; the median gets about half.</t>
   </si>
   <si>
-    <t xml:space="preserve">With the default equal weights, each part can add at most 100 / (number of parts with a number): 20 points when all five have one. A blank part has no number (for example, no award ceiling), and the others share its points.</t>
+    <t xml:space="preserve">With the default equal weights, each part can add at most 100 / (number of parts with a number): 20 points when all five have one. A blank part has no number, and the others share its points. People reached is blank when the population served has no NC count (people with a substance use disorder); help per person is blank when either the award or the people count is.</t>
   </si>
   <si>
     <t xml:space="preserve">Grants.gov ID is the number in grants.gov listing addresses; Simpler.Grants.gov ID is the code in the link, which opens the listing.</t>
@@ -122,7 +122,10 @@
     <t xml:space="preserve">Deadline (Grants.gov)</t>
   </si>
   <si>
-    <t xml:space="preserve">Award ceiling (Grants.gov)</t>
+    <t xml:space="preserve">Award per recipient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Award source</t>
   </si>
   <si>
     <t xml:space="preserve">Award floor (Grants.gov)</t>
@@ -137,12 +140,42 @@
     <t xml:space="preserve">DHHS</t>
   </si>
   <si>
+    <t xml:space="preserve">strong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All NC residents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public health preparedness, infectious disease and disaster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2e580529-c869-47d0-9aab-7d0e239ed5e8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrated Viral Hepatitis Surveillance, Testing, Treatment, and Prevention Programs for Health Departments (IVH-STTP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-CDC-NCHHSTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forecasted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate: total funding / expected awards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/2e580529-c869-47d0-9aab-7d0e239ed5e8</t>
+  </si>
+  <si>
     <t xml:space="preserve">partial</t>
   </si>
   <si>
-    <t xml:space="preserve">All NC residents</t>
-  </si>
-  <si>
     <t xml:space="preserve">Health access and workforce</t>
   </si>
   <si>
@@ -161,34 +194,25 @@
     <t xml:space="preserve">HHS-HRSA</t>
   </si>
   <si>
-    <t xml:space="preserve">forecasted</t>
+    <t xml:space="preserve">Grants.gov award ceiling</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/c30fddfd-2094-4cf0-ba21-04b6736fc755</t>
   </si>
   <si>
-    <t xml:space="preserve">strong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public health preparedness, infectious disease and disaster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2e580529-c869-47d0-9aab-7d0e239ed5e8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrated Viral Hepatitis Surveillance, Testing, Treatment, and Prevention Programs for Health Departments (IVH-STTP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-CDC-NCHHSTP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/2e580529-c869-47d0-9aab-7d0e239ed5e8</t>
+    <t xml:space="preserve">HRSA-27-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51fa7e21-beca-497f-a0f1-bf175382f77f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year (FY) 2027 Service Area Competition (SAC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/51fa7e21-beca-497f-a0f1-bf175382f77f</t>
   </si>
   <si>
     <t xml:space="preserve">CDC-RFA-CK-27-0007</t>
@@ -209,21 +233,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/38e79010-c2a9-4d5f-bf81-cede591318e4</t>
   </si>
   <si>
-    <t xml:space="preserve">HRSA-27-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51fa7e21-beca-497f-a0f1-bf175382f77f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiscal Year (FY) 2027 Service Area Competition (SAC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/51fa7e21-beca-497f-a0f1-bf175382f77f</t>
-  </si>
-  <si>
     <t xml:space="preserve">HRSA-27-008</t>
   </si>
   <si>
@@ -254,6 +263,57 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/be465a8b-8694-4eef-9801-5160a92c7cdf</t>
   </si>
   <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">362349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0ff3ace3-70fb-4ef7-b6ba-b93a899a2707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controlling and Preventing STIs in US Health Departments (CAP-STIs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/0ff3ace3-70fb-4ef7-b6ba-b93a899a2707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">People with a substance use disorder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">441d2761-0d9c-42ae-a3da-905ce4ed0ca4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strengthening Services to Prevent the Infectious Disease Consequences of Drug Use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/441d2761-0d9c-42ae-a3da-905ce4ed0ca4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">People without health insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1d55627c-531e-4a60-95e0-719b256179bf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIV Care Grant Program - Part B States/Territories Formula and AIDS Drug Assistance Program Formula and AIDS Drug Assistance Program Supplemental Awards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/1d55627c-531e-4a60-95e0-719b256179bf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adults with frequent mental distress</t>
   </si>
   <si>
@@ -293,6 +353,57 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/d9551b09-3a45-4dc1-a343-3f09521de9aa</t>
   </si>
   <si>
+    <t xml:space="preserve">CDC-RFA-DD-27-0065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91d0d477-b844-4189-8880-bd7a2876b24e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surveillance and Case Control Study of Stillbirth and Birth Defects (SUCCSSBD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-CDC-NCBDDD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/91d0d477-b844-4189-8880-bd7a2876b24e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e511b41d-655a-4869-bfd3-09fbf0c33987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holistic and Evidence-Informed Wellness for STI Prevention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/e511b41d-655a-4869-bfd3-09fbf0c33987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maternal, infant and reproductive health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-DD-27-0028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172926e9-5f18-4993-893d-ac73be5bbb9d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maternal-Child Surveillance and Partnerships for Action, Results, and Knowledge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/172926e9-5f18-4993-893d-ac73be5bbb9d</t>
+  </si>
+  <si>
     <t xml:space="preserve">RFA-IP-27-035</t>
   </si>
   <si>
@@ -314,6 +425,27 @@
     <t xml:space="preserve">Food and nutrition security</t>
   </si>
   <si>
+    <t xml:space="preserve">FOR-FD-23-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342630</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b8b51aae-68fc-448a-bbca-5fbfd229a841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufactured Foods Flexible Funding Model (MF-FFM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-FDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not stated (Grants.gov gives no total or no award count to estimate from)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b8b51aae-68fc-448a-bbca-5fbfd229a841</t>
+  </si>
+  <si>
     <t xml:space="preserve">HRSA-27-019</t>
   </si>
   <si>
@@ -347,9 +479,6 @@
     <t xml:space="preserve">Women who gave birth in the past year</t>
   </si>
   <si>
-    <t xml:space="preserve">Maternal, infant and reproductive health</t>
-  </si>
-  <si>
     <t xml:space="preserve">HRSA-27-047</t>
   </si>
   <si>
@@ -365,21 +494,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/741f2935-18c1-4e3e-8f54-f30dc3a6ee80</t>
   </si>
   <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">362349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0ff3ace3-70fb-4ef7-b6ba-b93a899a2707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controlling and Preventing STIs in US Health Departments (CAP-STIs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/0ff3ace3-70fb-4ef7-b6ba-b93a899a2707</t>
-  </si>
-  <si>
     <t xml:space="preserve">HRSA-27-046</t>
   </si>
   <si>
@@ -395,70 +509,19 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/6bc69d9c-87b7-4329-962c-16c8e3ad553d</t>
   </si>
   <si>
-    <t xml:space="preserve">CDC-RFA-DD-27-0065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91d0d477-b844-4189-8880-bd7a2876b24e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surveillance and Case Control Study of Stillbirth and Birth Defects (SUCCSSBD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-CDC-NCBDDD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/91d0d477-b844-4189-8880-bd7a2876b24e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-DD-27-0028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172926e9-5f18-4993-893d-ac73be5bbb9d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maternal-Child Surveillance and Partnerships for Action, Results, and Knowledge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/172926e9-5f18-4993-893d-ac73be5bbb9d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e511b41d-655a-4869-bfd3-09fbf0c33987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holistic and Evidence-Informed Wellness for STI Prevention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/e511b41d-655a-4869-bfd3-09fbf0c33987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOR-FD-23-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342630</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b8b51aae-68fc-448a-bbca-5fbfd229a841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manufactured Foods Flexible Funding Model (MF-FFM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-FDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b8b51aae-68fc-448a-bbca-5fbfd229a841</t>
+    <t xml:space="preserve">HRSA-27-079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a73919b2-7a90-4735-8ec5-a67c08dea3ed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan White HIV/AIDS Program (RWHAP) Integrated HIV/AIDS Planning Resource Allocation Cooperative Agreement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/a73919b2-7a90-4735-8ec5-a67c08dea3ed</t>
   </si>
   <si>
     <t xml:space="preserve">RFA-DP-27-051</t>
@@ -476,21 +539,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/54666d94-e0dc-44d3-90e6-6eb913f79ca9</t>
   </si>
   <si>
-    <t xml:space="preserve">HRSA-27-079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a73919b2-7a90-4735-8ec5-a67c08dea3ed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan White HIV/AIDS Program (RWHAP) Integrated HIV/AIDS Planning Resource Allocation Cooperative Agreement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/a73919b2-7a90-4735-8ec5-a67c08dea3ed</t>
-  </si>
-  <si>
     <t xml:space="preserve">RFA-OH-27-050</t>
   </si>
   <si>
@@ -536,24 +584,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/8bb15754-c013-462d-b305-f2a8dd116e08</t>
   </si>
   <si>
-    <t xml:space="preserve">People with a substance use disorder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">441d2761-0d9c-42ae-a3da-905ce4ed0ca4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strengthening Services to Prevent the Infectious Disease Consequences of Drug Use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/441d2761-0d9c-42ae-a3da-905ce4ed0ca4</t>
-  </si>
-  <si>
     <t xml:space="preserve">HRSA-27-039</t>
   </si>
   <si>
@@ -584,24 +614,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/18c0a9f1-fe39-4c7a-8ffd-1d8c656d666f</t>
   </si>
   <si>
-    <t xml:space="preserve">People without health insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1d55627c-531e-4a60-95e0-719b256179bf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIV Care Grant Program - Part B States/Territories Formula and AIDS Drug Assistance Program Formula and AIDS Drug Assistance Program Supplemental Awards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/1d55627c-531e-4a60-95e0-719b256179bf</t>
-  </si>
-  <si>
     <t xml:space="preserve">CDC-RFA-TP22-2201</t>
   </si>
   <si>
@@ -623,6 +635,72 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/42a1b238-2c19-47b4-ae58-f4a775231b78</t>
   </si>
   <si>
+    <t xml:space="preserve">CDC-RFA-DP-27-0043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">477f11ad-e8c7-40ea-84f3-f5bec6e50e3b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statewide Perinatal Quality Collaboratives: Improving Perinatal Care and Outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-CDC-NCCDPHP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/477f11ad-e8c7-40ea-84f3-f5bec6e50e3b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-2026-ACF-ORR-ZU-0019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">361822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cb2cbb9f-741d-4e6b-ad32-557d751f9903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home Study and Post-Release Services for Unaccompanied Alien Children​​</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-ACF-ORR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/cb2cbb9f-741d-4e6b-ad32-557d751f9903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-CK-26-035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">360199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10f4a697-e6a1-454a-bb73-74bc933f364a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emerging Infections Network - Research for Preventing, Detecting, and Managing Travel-associated Infectious Diseases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/10f4a697-e6a1-454a-bb73-74bc933f364a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-OH-24-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b307f2ac-767d-4715-be92-f5326db2cd9d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Center for Construction Safety and Health Research and Translation (U54)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b307f2ac-767d-4715-be92-f5326db2cd9d</t>
+  </si>
+  <si>
     <t xml:space="preserve">CDC-RFA-DP-27-0072</t>
   </si>
   <si>
@@ -635,58 +713,82 @@
     <t xml:space="preserve">Promoting Population Health through Increased Capacity in Alcohol Epidemiology &amp; the Prevention of Excessive Alcohol Use</t>
   </si>
   <si>
-    <t xml:space="preserve">HHS-CDC-NCCDPHP</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/6d44bb23-2a1f-4e12-8d72-c2b5b46195d4</t>
   </si>
   <si>
-    <t xml:space="preserve">HHS-2026-ACF-ORR-ZU-0019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">361822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cb2cbb9f-741d-4e6b-ad32-557d751f9903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Study and Post-Release Services for Unaccompanied Alien Children​​</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-ACF-ORR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/cb2cbb9f-741d-4e6b-ad32-557d751f9903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFA-CK-26-035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">360199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10f4a697-e6a1-454a-bb73-74bc933f364a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emerging Infections Network - Research for Preventing, Detecting, and Managing Travel-associated Infectious Diseases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/10f4a697-e6a1-454a-bb73-74bc933f364a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFA-OH-24-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b307f2ac-767d-4715-be92-f5326db2cd9d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Center for Construction Safety and Health Research and Translation (U54)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b307f2ac-767d-4715-be92-f5326db2cd9d</t>
+    <t xml:space="preserve">HRSA-27-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88f12b64-0fbc-44ea-a689-57ed9e9fb9dd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year (FY) 2027 State and Regional Primary Care Association (PCA) Cooperative Agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/88f12b64-0fbc-44ea-a689-57ed9e9fb9dd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-DP-27-036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5686905a-446f-4b0d-8885-e1683d35c3f4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilot Testing, Implementation, and Evaluation of the Cervical, Breast and Colorectal Cancer Clinical Decision Support Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/5686905a-446f-4b0d-8885-e1683d35c3f4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44a089ce-dd0a-4cde-b6f4-c77d08d56a08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Communities Opioid Response Program - Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/44a089ce-dd0a-4cde-b6f4-c77d08d56a08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">910a75ad-0418-4091-a436-703280874498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infant-Toddler Court Program–National Resource Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/910a75ad-0418-4091-a436-703280874498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b9bdeaa2-068f-4aa9-960a-948c0b0a9bfd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Home Visiting Research, Improvement, Sustainability and Evaluation Center (HV-RISE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b9bdeaa2-068f-4aa9-960a-948c0b0a9bfd</t>
   </si>
   <si>
     <t xml:space="preserve">HRSA-27-042</t>
@@ -704,21 +806,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/02b2d236-f596-4aca-874d-b8e364156ddc</t>
   </si>
   <si>
-    <t xml:space="preserve">HRSA-27-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88f12b64-0fbc-44ea-a689-57ed9e9fb9dd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiscal Year (FY) 2027 State and Regional Primary Care Association (PCA) Cooperative Agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/88f12b64-0fbc-44ea-a689-57ed9e9fb9dd</t>
-  </si>
-  <si>
     <t xml:space="preserve">CDC-RFA-CE-27-0024</t>
   </si>
   <si>
@@ -737,49 +824,34 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/3c36bc50-73ae-42ad-a727-fae640dad5c9</t>
   </si>
   <si>
-    <t xml:space="preserve">HRSA-27-020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">910a75ad-0418-4091-a436-703280874498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infant-Toddler Court Program–National Resource Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/910a75ad-0418-4091-a436-703280874498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44a089ce-dd0a-4cde-b6f4-c77d08d56a08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Communities Opioid Response Program - Evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/44a089ce-dd0a-4cde-b6f4-c77d08d56a08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b9bdeaa2-068f-4aa9-960a-948c0b0a9bfd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Home Visiting Research, Improvement, Sustainability and Evaluation Center (HV-RISE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b9bdeaa2-068f-4aa9-960a-948c0b0a9bfd</t>
+    <t xml:space="preserve">CDC-RFA-PS-27-0011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f931e3f2-28c6-4bcb-83ff-894bc6b2266c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Viral Hepatitis Education, Awareness, and Capacity Building for Communities and Providers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/f931e3f2-28c6-4bcb-83ff-894bc6b2266c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3fe27753-0c94-4aa0-b7fb-09712631f269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infant-Toddler Court Program–State Awards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/3fe27753-0c94-4aa0-b7fb-09712631f269</t>
   </si>
   <si>
     <t xml:space="preserve">RFA-OH-27-049</t>
@@ -797,19 +869,52 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/43e32c6d-fbbd-4056-8fd4-f64cdebefd41</t>
   </si>
   <si>
-    <t xml:space="preserve">HRSA-27-021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3fe27753-0c94-4aa0-b7fb-09712631f269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infant-Toddler Court Program–State Awards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/3fe27753-0c94-4aa0-b7fb-09712631f269</t>
+    <t xml:space="preserve">CDC-RFA-CE-27-0039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23b80a6d-ae96-4b02-b4ae-69093f8939d5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core State Injury Prevention Program (Core SIPP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/23b80a6d-ae96-4b02-b4ae-69093f8939d5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06024144-a58a-42d8-8813-75357d9bb7fe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonstration Projects for Whole-Person Health Models for Women Living with HIV in the South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/06024144-a58a-42d8-8813-75357d9bb7fe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHS-26-MT-144-000-99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">363151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4802584e-01a8-4435-9ce9-710fbc85cba0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year 2026 Flood Mitigation Assistance Swift Current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHS-DHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/4802584e-01a8-4435-9ce9-710fbc85cba0</t>
   </si>
   <si>
     <t xml:space="preserve">RFA-CK-26-036</t>
@@ -842,84 +947,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/9accc70c-9683-4b78-bb7b-e8fdbcff1b47</t>
   </si>
   <si>
-    <t xml:space="preserve">CDC-RFA-CE-27-0039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23b80a6d-ae96-4b02-b4ae-69093f8939d5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core State Injury Prevention Program (Core SIPP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/23b80a6d-ae96-4b02-b4ae-69093f8939d5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFA-DP-27-036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5686905a-446f-4b0d-8885-e1683d35c3f4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pilot Testing, Implementation, and Evaluation of the Cervical, Breast and Colorectal Cancer Clinical Decision Support Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/5686905a-446f-4b0d-8885-e1683d35c3f4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f931e3f2-28c6-4bcb-83ff-894bc6b2266c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Viral Hepatitis Education, Awareness, and Capacity Building for Communities and Providers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/f931e3f2-28c6-4bcb-83ff-894bc6b2266c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHS-26-MT-144-000-99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4802584e-01a8-4435-9ce9-710fbc85cba0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiscal Year 2026 Flood Mitigation Assistance Swift Current</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHS-DHS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/4802584e-01a8-4435-9ce9-710fbc85cba0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-DP-27-0043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363330</t>
-  </si>
-  <si>
-    <t xml:space="preserve">477f11ad-e8c7-40ea-84f3-f5bec6e50e3b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statewide Perinatal Quality Collaboratives: Improving Perinatal Care and Outcomes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/477f11ad-e8c7-40ea-84f3-f5bec6e50e3b</t>
-  </si>
-  <si>
     <t xml:space="preserve">RFA-OH-25-003</t>
   </si>
   <si>
@@ -948,21 +975,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/f2ea8925-6244-47e8-8de5-ffe0007096e7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">363389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06024144-a58a-42d8-8813-75357d9bb7fe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demonstration Projects for Whole-Person Health Models for Women Living with HIV in the South</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/06024144-a58a-42d8-8813-75357d9bb7fe</t>
   </si>
   <si>
     <t xml:space="preserve">Veterans</t>
@@ -1596,9 +1608,10 @@
     <col min="20" max="20" width="11.71" hidden="0" customWidth="1"/>
     <col min="21" max="21" width="13.71" hidden="0" customWidth="1"/>
     <col min="22" max="22" width="14.71" hidden="0" customWidth="1"/>
-    <col min="23" max="23" width="13.71" hidden="0" customWidth="1"/>
-    <col min="24" max="24" width="55.71" hidden="0" customWidth="1"/>
-    <col min="25" max="25" width="30.71" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="24.71" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="13.71" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="55.71" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="30.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1677,43 +1690,46 @@
       <c r="Y1" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="Z1" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10584340</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2" s="8" t="n">
         <v>13</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>2.08</v>
+        <v>0.71</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>16.9</v>
+        <v>13</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>19.6</v>
+        <v>18.1</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>1</v>
@@ -1722,40 +1738,41 @@
         <v>6.7</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>46386</v>
+        <v>46434</v>
       </c>
       <c r="V2" s="5" t="n">
-        <v>22024900</v>
-      </c>
-      <c r="W2" s="5" t="n">
-        <v>398400</v>
-      </c>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="10" t="s">
-        <v>48</v>
+        <v>7500000</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="10" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -1764,63 +1781,76 @@
         <v>66</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>33.3</v>
+        <v>10</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10584340</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
+        <v>13</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>19.6</v>
+      </c>
       <c r="L3" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>46434</v>
-      </c>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="10" t="s">
-        <v>56</v>
+        <v>46386</v>
+      </c>
+      <c r="V3" s="5" t="n">
+        <v>22024900</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X3" s="5" t="n">
+        <v>398400</v>
+      </c>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="10" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -1829,7 +1859,7 @@
         <v>65</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E4" s="8" t="n">
         <v>10</v>
@@ -1838,22 +1868,22 @@
         <v>10584340</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H4" s="8" t="n">
         <v>13</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>1</v>
@@ -1862,49 +1892,52 @@
         <v>6.7</v>
       </c>
       <c r="O4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="S4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="T4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>46386</v>
+      </c>
+      <c r="V4" s="5" t="n">
+        <v>19182000</v>
+      </c>
+      <c r="W4" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>46391</v>
-      </c>
-      <c r="V4" s="5" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="W4" s="5" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="10" t="s">
-        <v>62</v>
+      <c r="X4" s="5" t="n">
+        <v>1215700</v>
+      </c>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="10" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>10</v>
@@ -1913,22 +1946,22 @@
         <v>10584340</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>13</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>15.6</v>
+        <v>16.3</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>1</v>
@@ -1937,40 +1970,43 @@
         <v>6.7</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>46386</v>
+        <v>46391</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>19182000</v>
-      </c>
-      <c r="W5" s="5" t="n">
-        <v>1215700</v>
-      </c>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="10" t="s">
-        <v>67</v>
+        <v>22000000</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X5" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="10" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>5</v>
@@ -1979,7 +2015,7 @@
         <v>64</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>10</v>
@@ -1988,7 +2024,7 @@
         <v>10584340</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>13</v>
@@ -2003,7 +2039,7 @@
         <v>19.1</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>1</v>
@@ -2012,22 +2048,22 @@
         <v>6.7</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>46395</v>
@@ -2035,26 +2071,29 @@
       <c r="V6" s="5" t="n">
         <v>15335500</v>
       </c>
-      <c r="W6" s="5" t="n">
+      <c r="W6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X6" s="5" t="n">
         <v>567000</v>
       </c>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="10" t="s">
-        <v>71</v>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="10" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>10</v>
@@ -2063,7 +2102,7 @@
         <v>10584340</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>13</v>
@@ -2072,13 +2111,13 @@
         <v>0.85</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>18.5</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>1</v>
@@ -2087,22 +2126,22 @@
         <v>6.7</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>46461</v>
@@ -2110,48 +2149,51 @@
       <c r="V7" s="5" t="n">
         <v>9000000</v>
       </c>
-      <c r="W7" s="5"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="10" t="s">
-        <v>77</v>
+      <c r="W7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="10" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>10</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1402172</v>
+        <v>10584340</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>2.7</v>
+        <v>13</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>7.13</v>
+        <v>0.8</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>18.7</v>
+        <v>13.3</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>1</v>
@@ -2160,146 +2202,142 @@
         <v>6.7</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>46328</v>
+        <v>46398</v>
       </c>
       <c r="V8" s="5" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="W8" s="5"/>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="10" t="s">
-        <v>83</v>
+        <v>8474576.27118644</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="10" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>2322823</v>
-      </c>
+        <v>16.7</v>
+      </c>
+      <c r="F9" s="6"/>
       <c r="G9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>17.8</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="H9" s="8"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="8"/>
       <c r="K9" s="8" t="n">
-        <v>17.6</v>
+        <v>33</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>6.7</v>
+        <v>11.1</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>46407</v>
+        <v>46531</v>
       </c>
       <c r="V9" s="5" t="n">
-        <v>5149000</v>
-      </c>
-      <c r="W9" s="5" t="n">
-        <v>5149000</v>
-      </c>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="10" t="s">
-        <v>90</v>
+        <v>41250000</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="10" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>10</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>10584340</v>
+        <v>1073923</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>13</v>
+        <v>1.3</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.11</v>
+        <v>20.22</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>8.9</v>
+        <v>19.3</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>14.6</v>
+        <v>19.3</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>1</v>
@@ -2308,73 +2346,74 @@
         <v>6.7</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>46387</v>
       </c>
       <c r="V10" s="5" t="n">
-        <v>1140000</v>
-      </c>
-      <c r="W10" s="5" t="n">
-        <v>850000</v>
-      </c>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="10" t="s">
-        <v>96</v>
+        <v>21716666.6666667</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="9"/>
+      <c r="Z10" s="10" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="E11" s="8" t="n">
         <v>10</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>10584340</v>
+        <v>1402172</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>13</v>
+        <v>2.7</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0.09</v>
+        <v>7.13</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>7.6</v>
+        <v>18.2</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>13.8</v>
+        <v>18.7</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>1</v>
@@ -2383,73 +2422,74 @@
         <v>6.7</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>46357</v>
+        <v>46328</v>
       </c>
       <c r="V11" s="5" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="W11" s="5" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="10" t="s">
-        <v>102</v>
+        <v>10000000</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="9"/>
+      <c r="Z11" s="10" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>10</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>10584340</v>
+        <v>2322823</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>13</v>
+        <v>4.7</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.09</v>
+        <v>2.22</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>7.6</v>
+        <v>17.5</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>13.8</v>
+        <v>17.6</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>1</v>
@@ -2458,73 +2498,76 @@
         <v>6.7</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>46438</v>
+        <v>46407</v>
       </c>
       <c r="V12" s="5" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="W12" s="5" t="n">
-        <v>350000</v>
-      </c>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="10" t="s">
-        <v>107</v>
+        <v>5149000</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X12" s="5" t="n">
+        <v>5149000</v>
+      </c>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="10" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E13" s="8" t="n">
         <v>10</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>127227</v>
+        <v>10584340</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.3</v>
+        <v>13</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>7.86</v>
+        <v>0.26</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>19.1</v>
+        <v>10</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>13.8</v>
+        <v>15.9</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>1</v>
@@ -2533,112 +2576,126 @@
         <v>6.7</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>46497</v>
+        <v>46477</v>
       </c>
       <c r="V13" s="5" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="W13" s="5"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="10" t="s">
-        <v>114</v>
+        <v>2750000</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="9"/>
+      <c r="Z13" s="10" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10584340</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I14" s="7"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
+        <v>13</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>16.2</v>
+      </c>
       <c r="L14" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>46398</v>
-      </c>
-      <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="10" t="s">
-        <v>119</v>
+        <v>46538</v>
+      </c>
+      <c r="V14" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="9"/>
+      <c r="Z14" s="10" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E15" s="8" t="n">
         <v>10</v>
@@ -2647,22 +2704,22 @@
         <v>10584340</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>13</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.07</v>
+        <v>0.21</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>6.2</v>
+        <v>9.1</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>12.8</v>
+        <v>15.5</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>1</v>
@@ -2671,103 +2728,119 @@
         <v>6.7</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>46464</v>
+        <v>46503</v>
       </c>
       <c r="V15" s="5" t="n">
-        <v>750000</v>
-      </c>
-      <c r="W15" s="5"/>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="10" t="s">
-        <v>124</v>
+        <v>2217391.30434783</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="10" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10584340</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I16" s="7"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
+        <v>13</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>12.7</v>
+      </c>
       <c r="L16" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>46477</v>
-      </c>
-      <c r="V16" s="5"/>
-      <c r="W16" s="5"/>
-      <c r="X16" s="9"/>
-      <c r="Y16" s="10" t="s">
-        <v>130</v>
+        <v>46387</v>
+      </c>
+      <c r="V16" s="5" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X16" s="5" t="n">
+        <v>850000</v>
+      </c>
+      <c r="Y16" s="9"/>
+      <c r="Z16" s="10" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>16</v>
@@ -2776,7 +2849,7 @@
         <v>49</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>16.7</v>
@@ -2785,7 +2858,7 @@
         <v>10584340</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>21.7</v>
@@ -2794,7 +2867,7 @@
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="2" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>1</v>
@@ -2803,197 +2876,226 @@
         <v>11.1</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="U17" s="4" t="n">
-        <v>46503</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="U17" s="4"/>
       <c r="V17" s="5"/>
-      <c r="W17" s="5"/>
-      <c r="X17" s="9"/>
-      <c r="Y17" s="10" t="s">
-        <v>135</v>
+      <c r="W17" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="X17" s="5"/>
+      <c r="Y17" s="9"/>
+      <c r="Z17" s="10" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10584340</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I18" s="7"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
+        <v>13</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>11.9</v>
+      </c>
       <c r="L18" s="2" t="s">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="8" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>46538</v>
-      </c>
-      <c r="V18" s="5"/>
-      <c r="W18" s="5"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="10" t="s">
-        <v>140</v>
+        <v>46357</v>
+      </c>
+      <c r="V18" s="5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X18" s="5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Y18" s="9"/>
+      <c r="Z18" s="10" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10584340</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I19" s="7"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
+        <v>13</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>11.9</v>
+      </c>
       <c r="L19" s="2" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>145</v>
+        <v>47</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="U19" s="4"/>
-      <c r="V19" s="5"/>
-      <c r="W19" s="5"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="10" t="s">
-        <v>146</v>
+        <v>48</v>
+      </c>
+      <c r="U19" s="4" t="n">
+        <v>46438</v>
+      </c>
+      <c r="V19" s="5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X19" s="5" t="n">
+        <v>350000</v>
+      </c>
+      <c r="Y19" s="9"/>
+      <c r="Z19" s="10" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>10</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>10584340</v>
+        <v>127227</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>40</v>
+        <v>152</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>13</v>
+        <v>0.3</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>0.07</v>
+        <v>7.86</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>5.8</v>
+        <v>18.6</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>1</v>
@@ -3002,49 +3104,50 @@
         <v>6.7</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>46468</v>
+        <v>46497</v>
       </c>
       <c r="V20" s="5" t="n">
-        <v>725000</v>
-      </c>
-      <c r="W20" s="5" t="n">
-        <v>500000</v>
-      </c>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="10" t="s">
-        <v>151</v>
+        <v>1000000</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X20" s="5"/>
+      <c r="Y20" s="9"/>
+      <c r="Z20" s="10" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E21" s="8" t="n">
         <v>10</v>
@@ -3053,7 +3156,7 @@
         <v>10584340</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>13</v>
@@ -3062,13 +3165,13 @@
         <v>0.07</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>11.9</v>
+        <v>10.6</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>1</v>
@@ -3077,47 +3180,50 @@
         <v>6.7</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>46405</v>
+        <v>46464</v>
       </c>
       <c r="V21" s="5" t="n">
-        <v>700000</v>
-      </c>
-      <c r="W21" s="5"/>
-      <c r="X21" s="9"/>
-      <c r="Y21" s="10" t="s">
-        <v>156</v>
+        <v>750000</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="9"/>
+      <c r="Z21" s="10" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>10</v>
@@ -3126,22 +3232,22 @@
         <v>10584340</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>13</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>11.6</v>
+        <v>9.6</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>1</v>
@@ -3150,49 +3256,50 @@
         <v>6.7</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>46386</v>
+        <v>46405</v>
       </c>
       <c r="V22" s="5" t="n">
-        <v>685000</v>
-      </c>
-      <c r="W22" s="5" t="n">
-        <v>150000</v>
-      </c>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="10" t="s">
-        <v>161</v>
+        <v>700000</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="10" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E23" s="8" t="n">
         <v>10</v>
@@ -3201,22 +3308,22 @@
         <v>10584340</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>13</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>11.4</v>
+        <v>10</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>1</v>
@@ -3225,47 +3332,52 @@
         <v>6.7</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>46</v>
+        <v>132</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>46466</v>
+        <v>46468</v>
       </c>
       <c r="V23" s="5" t="n">
-        <v>650000</v>
-      </c>
-      <c r="W23" s="5"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="10" t="s">
-        <v>166</v>
+        <v>725000</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X23" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="10" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>10</v>
@@ -3274,22 +3386,22 @@
         <v>10584340</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>13</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>1</v>
@@ -3298,40 +3410,43 @@
         <v>6.7</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>46</v>
+        <v>132</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>46462</v>
+        <v>46386</v>
       </c>
       <c r="V24" s="5" t="n">
-        <v>500000</v>
-      </c>
-      <c r="W24" s="5" t="n">
-        <v>300000</v>
-      </c>
-      <c r="X24" s="9"/>
-      <c r="Y24" s="10" t="s">
-        <v>171</v>
+        <v>685000</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X24" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Y24" s="9"/>
+      <c r="Z24" s="10" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>24</v>
@@ -3340,68 +3455,83 @@
         <v>42</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="F25" s="6"/>
+        <v>10</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>10584340</v>
+      </c>
       <c r="G25" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H25" s="8"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
+        <v>41</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>9.2</v>
+      </c>
       <c r="L25" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>16.7</v>
+        <v>6.7</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>46531</v>
-      </c>
-      <c r="V25" s="5"/>
-      <c r="W25" s="5"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="10" t="s">
-        <v>177</v>
+        <v>46466</v>
+      </c>
+      <c r="V25" s="5" t="n">
+        <v>650000</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X25" s="5"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="10" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>10</v>
@@ -3410,7 +3540,7 @@
         <v>10584340</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H26" s="8" t="n">
         <v>13</v>
@@ -3419,13 +3549,13 @@
         <v>0.05</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>1</v>
@@ -3434,49 +3564,52 @@
         <v>6.7</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>46532</v>
+        <v>46462</v>
       </c>
       <c r="V26" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="W26" s="5" t="n">
-        <v>250000</v>
-      </c>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="10" t="s">
-        <v>182</v>
+      <c r="W26" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X26" s="5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="10" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E27" s="8" t="n">
         <v>10</v>
@@ -3485,22 +3618,22 @@
         <v>10584340</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>13</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>5.2</v>
+        <v>6.9</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>1</v>
@@ -3509,130 +3642,146 @@
         <v>6.7</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>46508</v>
+        <v>46532</v>
       </c>
       <c r="V27" s="5" t="n">
-        <v>300000</v>
-      </c>
-      <c r="W27" s="5"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="10" t="s">
-        <v>187</v>
+        <v>500000</v>
+      </c>
+      <c r="W27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X27" s="5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="10" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>1073923</v>
+        <v>10584340</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>188</v>
+        <v>41</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I28" s="7"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
+        <v>13</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K28" s="8" t="n">
+        <v>3.9</v>
+      </c>
       <c r="L28" s="2" t="s">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>46387</v>
-      </c>
-      <c r="V28" s="5"/>
-      <c r="W28" s="5"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="10" t="s">
-        <v>193</v>
+        <v>46508</v>
+      </c>
+      <c r="V28" s="5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="W28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X28" s="5"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="10" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y28"/>
+  <autoFilter ref="A1:Z28"/>
   <hyperlinks>
-    <hyperlink ref="Y2" r:id="rId1h"/>
-    <hyperlink ref="Y3" r:id="rId2h"/>
-    <hyperlink ref="Y4" r:id="rId3h"/>
-    <hyperlink ref="Y5" r:id="rId4h"/>
-    <hyperlink ref="Y6" r:id="rId5h"/>
-    <hyperlink ref="Y7" r:id="rId6h"/>
-    <hyperlink ref="Y8" r:id="rId7h"/>
-    <hyperlink ref="Y9" r:id="rId8h"/>
-    <hyperlink ref="Y10" r:id="rId9h"/>
-    <hyperlink ref="Y11" r:id="rId10h"/>
-    <hyperlink ref="Y12" r:id="rId11h"/>
-    <hyperlink ref="Y13" r:id="rId12h"/>
-    <hyperlink ref="Y14" r:id="rId13h"/>
-    <hyperlink ref="Y15" r:id="rId14h"/>
-    <hyperlink ref="Y16" r:id="rId15h"/>
-    <hyperlink ref="Y17" r:id="rId16h"/>
-    <hyperlink ref="Y18" r:id="rId17h"/>
-    <hyperlink ref="Y19" r:id="rId18h"/>
-    <hyperlink ref="Y20" r:id="rId19h"/>
-    <hyperlink ref="Y21" r:id="rId20h"/>
-    <hyperlink ref="Y22" r:id="rId21h"/>
-    <hyperlink ref="Y23" r:id="rId22h"/>
-    <hyperlink ref="Y24" r:id="rId23h"/>
-    <hyperlink ref="Y25" r:id="rId24h"/>
-    <hyperlink ref="Y26" r:id="rId25h"/>
-    <hyperlink ref="Y27" r:id="rId26h"/>
-    <hyperlink ref="Y28" r:id="rId27h"/>
+    <hyperlink ref="Z2" r:id="rId1h"/>
+    <hyperlink ref="Z3" r:id="rId2h"/>
+    <hyperlink ref="Z4" r:id="rId3h"/>
+    <hyperlink ref="Z5" r:id="rId4h"/>
+    <hyperlink ref="Z6" r:id="rId5h"/>
+    <hyperlink ref="Z7" r:id="rId6h"/>
+    <hyperlink ref="Z8" r:id="rId7h"/>
+    <hyperlink ref="Z9" r:id="rId8h"/>
+    <hyperlink ref="Z10" r:id="rId9h"/>
+    <hyperlink ref="Z11" r:id="rId10h"/>
+    <hyperlink ref="Z12" r:id="rId11h"/>
+    <hyperlink ref="Z13" r:id="rId12h"/>
+    <hyperlink ref="Z14" r:id="rId13h"/>
+    <hyperlink ref="Z15" r:id="rId14h"/>
+    <hyperlink ref="Z16" r:id="rId15h"/>
+    <hyperlink ref="Z17" r:id="rId16h"/>
+    <hyperlink ref="Z18" r:id="rId17h"/>
+    <hyperlink ref="Z19" r:id="rId18h"/>
+    <hyperlink ref="Z20" r:id="rId19h"/>
+    <hyperlink ref="Z21" r:id="rId20h"/>
+    <hyperlink ref="Z22" r:id="rId21h"/>
+    <hyperlink ref="Z23" r:id="rId22h"/>
+    <hyperlink ref="Z24" r:id="rId23h"/>
+    <hyperlink ref="Z25" r:id="rId24h"/>
+    <hyperlink ref="Z26" r:id="rId25h"/>
+    <hyperlink ref="Z27" r:id="rId26h"/>
+    <hyperlink ref="Z28" r:id="rId27h"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3666,9 +3815,10 @@
     <col min="20" max="20" width="11.71" hidden="0" customWidth="1"/>
     <col min="21" max="21" width="13.71" hidden="0" customWidth="1"/>
     <col min="22" max="22" width="14.71" hidden="0" customWidth="1"/>
-    <col min="23" max="23" width="13.71" hidden="0" customWidth="1"/>
-    <col min="24" max="24" width="55.71" hidden="0" customWidth="1"/>
-    <col min="25" max="25" width="30.71" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="24.71" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="13.71" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="55.71" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="30.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3747,10 +3897,13 @@
       <c r="Y1" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="Z1" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -3759,7 +3912,7 @@
         <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E2" s="13" t="n">
         <v>20</v>
@@ -3768,7 +3921,7 @@
         <v>10584340</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2" s="13" t="n">
         <v>13</v>
@@ -3777,13 +3930,13 @@
         <v>0.47</v>
       </c>
       <c r="J2" s="13" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="K2" s="13" t="n">
         <v>17.3</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>1</v>
@@ -3792,22 +3945,22 @@
         <v>6.7</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>46429</v>
@@ -3815,82 +3968,96 @@
       <c r="V2" s="5" t="n">
         <v>5000000</v>
       </c>
-      <c r="W2" s="5" t="n">
+      <c r="W2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X2" s="5" t="n">
         <v>50000</v>
       </c>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="10" t="s">
-        <v>200</v>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="10" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>10584340</v>
+        <v>127227</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>40</v>
+        <v>152</v>
       </c>
       <c r="H3" s="13" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I3" s="12"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+        <v>0.3</v>
+      </c>
+      <c r="I3" s="12" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="J3" s="13" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="K3" s="13" t="n">
+        <v>15.3</v>
+      </c>
       <c r="L3" s="2" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N3" s="13" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>46507</v>
-      </c>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="10" t="s">
-        <v>206</v>
+        <v>46510</v>
+      </c>
+      <c r="V3" s="5" t="n">
+        <v>2141025.64102564</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="10" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -3899,7 +4066,7 @@
         <v>61</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E4" s="13" t="n">
         <v>10</v>
@@ -3908,7 +4075,7 @@
         <v>2322823</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="H4" s="13" t="n">
         <v>4.7</v>
@@ -3923,7 +4090,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>1</v>
@@ -3932,22 +4099,22 @@
         <v>6.7</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>46661</v>
@@ -3955,17 +4122,20 @@
       <c r="V4" s="5" t="n">
         <v>100000000</v>
       </c>
-      <c r="W4" s="5" t="n">
+      <c r="W4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X4" s="5" t="n">
         <v>1000000</v>
       </c>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="10" t="s">
-        <v>212</v>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="10" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>4</v>
@@ -3974,7 +4144,7 @@
         <v>60</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>10</v>
@@ -3983,7 +4153,7 @@
         <v>10584340</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H5" s="13" t="n">
         <v>13</v>
@@ -3992,13 +4162,13 @@
         <v>0.57</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="K5" s="13" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>1</v>
@@ -4007,22 +4177,22 @@
         <v>6.7</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="U5" s="4" t="n">
         <v>46331</v>
@@ -4030,17 +4200,20 @@
       <c r="V5" s="5" t="n">
         <v>6000000</v>
       </c>
-      <c r="W5" s="5" t="n">
+      <c r="W5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X5" s="5" t="n">
         <v>1750000</v>
       </c>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="10" t="s">
-        <v>217</v>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="10" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>5</v>
@@ -4049,7 +4222,7 @@
         <v>60</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>10</v>
@@ -4058,7 +4231,7 @@
         <v>10584340</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H6" s="13" t="n">
         <v>13</v>
@@ -4067,13 +4240,13 @@
         <v>0.54</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="K6" s="13" t="n">
         <v>17.7</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>1</v>
@@ -4082,22 +4255,22 @@
         <v>6.7</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>46357</v>
@@ -4105,17 +4278,20 @@
       <c r="V6" s="5" t="n">
         <v>5750000</v>
       </c>
-      <c r="W6" s="5" t="n">
+      <c r="W6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X6" s="5" t="n">
         <v>3000000</v>
       </c>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="10" t="s">
-        <v>222</v>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="10" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>6</v>
@@ -4124,63 +4300,74 @@
         <v>59</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="F7" s="11"/>
+        <v>20</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>10584340</v>
+      </c>
       <c r="G7" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="13"/>
+        <v>41</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>6.7</v>
+      </c>
       <c r="K7" s="13" t="n">
-        <v>14.9</v>
+        <v>12.4</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N7" s="13" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>46</v>
+        <v>209</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>46483</v>
+        <v>46507</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>500000</v>
-      </c>
-      <c r="W7" s="5"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="10" t="s">
-        <v>227</v>
+        <v>1002916.66666667</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="10" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
@@ -4189,7 +4376,7 @@
         <v>58</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>10</v>
@@ -4198,7 +4385,7 @@
         <v>10584340</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H8" s="13" t="n">
         <v>13</v>
@@ -4210,10 +4397,10 @@
         <v>11.6</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>1</v>
@@ -4222,22 +4409,22 @@
         <v>6.7</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U8" s="4" t="n">
         <v>46412</v>
@@ -4245,17 +4432,20 @@
       <c r="V8" s="5" t="n">
         <v>4900000</v>
       </c>
-      <c r="W8" s="5" t="n">
+      <c r="W8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X8" s="5" t="n">
         <v>790000</v>
       </c>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="10" t="s">
-        <v>232</v>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="10" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>8</v>
@@ -4264,31 +4454,31 @@
         <v>58</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1402172</v>
+        <v>10584340</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>2.7</v>
+        <v>13</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>0.86</v>
+        <v>0.34</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>13.8</v>
+        <v>11.2</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>14.8</v>
+        <v>16.8</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>1</v>
@@ -4297,115 +4487,111 @@
         <v>6.7</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>237</v>
+        <v>132</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>46494</v>
+        <v>46469</v>
       </c>
       <c r="V9" s="5" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="W9" s="5" t="n">
-        <v>650000</v>
-      </c>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="10" t="s">
-        <v>238</v>
+        <v>3625000</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="10" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>2322823</v>
-      </c>
+        <v>16.7</v>
+      </c>
+      <c r="F10" s="11"/>
       <c r="G10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H10" s="13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I10" s="12" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>18.2</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="H10" s="13"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="13"/>
       <c r="K10" s="13" t="n">
-        <v>18.1</v>
+        <v>28.9</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="13" t="n">
-        <v>6.7</v>
+        <v>11.1</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>46498</v>
+        <v>46469</v>
       </c>
       <c r="V10" s="5" t="n">
-        <v>6750000</v>
-      </c>
-      <c r="W10" s="5" t="n">
-        <v>6750000</v>
-      </c>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="10" t="s">
-        <v>243</v>
+        <v>5000000</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X10" s="5" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="Y10" s="9"/>
+      <c r="Z10" s="10" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>10</v>
@@ -4414,65 +4600,76 @@
         <v>57</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F11" s="11"/>
+        <v>10</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>2322823</v>
+      </c>
       <c r="G11" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="13"/>
+        <v>104</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>17.9</v>
+      </c>
       <c r="K11" s="13" t="n">
-        <v>28.8</v>
+        <v>18</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="13" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>46469</v>
+        <v>46498</v>
       </c>
       <c r="V11" s="5" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="W11" s="5" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="10" t="s">
-        <v>248</v>
+        <v>6750000</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X11" s="5" t="n">
+        <v>6750000</v>
+      </c>
+      <c r="Y11" s="9"/>
+      <c r="Z11" s="10" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>11</v>
@@ -4481,7 +4678,7 @@
         <v>56</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E12" s="13" t="n">
         <v>10</v>
@@ -4490,7 +4687,7 @@
         <v>2322823</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="H12" s="13" t="n">
         <v>4.7</v>
@@ -4499,13 +4696,13 @@
         <v>2.15</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="K12" s="13" t="n">
         <v>17.3</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>1</v>
@@ -4514,22 +4711,22 @@
         <v>6.7</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>46441</v>
@@ -4537,125 +4734,121 @@
       <c r="V12" s="5" t="n">
         <v>5000000</v>
       </c>
-      <c r="W12" s="5" t="n">
+      <c r="W12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X12" s="5" t="n">
         <v>5000000</v>
       </c>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="10" t="s">
-        <v>253</v>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="10" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>10584340</v>
-      </c>
+        <v>33.3</v>
+      </c>
+      <c r="F13" s="11"/>
       <c r="G13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>9.3</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="H13" s="13"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="13"/>
       <c r="K13" s="13" t="n">
-        <v>15.2</v>
+        <v>11.6</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>6.7</v>
+        <v>11.1</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>46444</v>
+        <v>46483</v>
       </c>
       <c r="V13" s="5" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="W13" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="10" t="s">
-        <v>258</v>
+      <c r="W13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="9"/>
+      <c r="Z13" s="10" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E14" s="13" t="n">
         <v>20</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>2322823</v>
+        <v>1402172</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>0.3</v>
+        <v>0.86</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>11.1</v>
+        <v>14</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>11.9</v>
+        <v>13</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>1</v>
@@ -4664,49 +4857,52 @@
         <v>6.7</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>46</v>
+        <v>266</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>46498</v>
+        <v>46494</v>
       </c>
       <c r="V14" s="5" t="n">
-        <v>700000</v>
-      </c>
-      <c r="W14" s="5" t="n">
-        <v>700000</v>
-      </c>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="10" t="s">
-        <v>263</v>
+        <v>1200000</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X14" s="5" t="n">
+        <v>650000</v>
+      </c>
+      <c r="Y14" s="9"/>
+      <c r="Z14" s="10" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>10</v>
@@ -4715,22 +4911,22 @@
         <v>10584340</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H15" s="13" t="n">
         <v>13</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>13.8</v>
+        <v>15.9</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>1</v>
@@ -4739,73 +4935,74 @@
         <v>6.7</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>199</v>
+        <v>48</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>46331</v>
+        <v>46539</v>
       </c>
       <c r="V15" s="5" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="W15" s="5" t="n">
-        <v>750000</v>
-      </c>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="10" t="s">
-        <v>268</v>
+        <v>2750000</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="10" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>10584340</v>
+        <v>2322823</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>13</v>
+        <v>4.7</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>0.09</v>
+        <v>0.3</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>6.7</v>
+        <v>10.9</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>13.3</v>
+        <v>9.6</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>1</v>
@@ -4814,235 +5011,273 @@
         <v>6.7</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>46455</v>
+        <v>46498</v>
       </c>
       <c r="V16" s="5" t="n">
-        <v>900000</v>
-      </c>
-      <c r="W16" s="5" t="n">
-        <v>450000</v>
-      </c>
-      <c r="X16" s="9"/>
-      <c r="Y16" s="10" t="s">
-        <v>273</v>
+        <v>700000</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X16" s="5" t="n">
+        <v>700000</v>
+      </c>
+      <c r="Y16" s="9"/>
+      <c r="Z16" s="10" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>10584340</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I17" s="12"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
+        <v>13</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>13.4</v>
+      </c>
       <c r="L17" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="13" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>237</v>
+        <v>132</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>46454</v>
-      </c>
-      <c r="V17" s="5"/>
-      <c r="W17" s="5"/>
-      <c r="X17" s="9"/>
-      <c r="Y17" s="10" t="s">
-        <v>278</v>
+        <v>46444</v>
+      </c>
+      <c r="V17" s="5" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X17" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="Y17" s="9"/>
+      <c r="Z17" s="10" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="F18" s="11" t="n">
         <v>10584340</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I18" s="12"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
+        <v>13</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>13.5</v>
+      </c>
       <c r="L18" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="13" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>95</v>
+        <v>266</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>46469</v>
-      </c>
-      <c r="V18" s="5"/>
-      <c r="W18" s="5"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="10" t="s">
-        <v>283</v>
+        <v>46454</v>
+      </c>
+      <c r="V18" s="5" t="n">
+        <v>1423076.92307692</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="9"/>
+      <c r="Z18" s="10" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>10584340</v>
+        <v>1402172</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I19" s="12"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
+        <v>2.7</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>15.7</v>
+      </c>
       <c r="L19" s="2" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="13" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>46539</v>
-      </c>
-      <c r="V19" s="5"/>
-      <c r="W19" s="5"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="10" t="s">
-        <v>288</v>
+        <v>46461</v>
+      </c>
+      <c r="V19" s="5" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="9"/>
+      <c r="Z19" s="10" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>19</v>
@@ -5051,7 +5286,7 @@
         <v>49</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E20" s="13" t="n">
         <v>16.7</v>
@@ -5060,7 +5295,7 @@
         <v>10584340</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H20" s="13" t="n">
         <v>21.7</v>
@@ -5069,7 +5304,7 @@
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
       <c r="L20" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>1</v>
@@ -5078,110 +5313,126 @@
         <v>11.1</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>46783</v>
       </c>
       <c r="V20" s="5"/>
-      <c r="W20" s="5"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="10" t="s">
-        <v>294</v>
+      <c r="W20" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="X20" s="5"/>
+      <c r="Y20" s="9"/>
+      <c r="Z20" s="10" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>33.3</v>
+        <v>10</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>127227</v>
+        <v>10584340</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I21" s="12"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
+        <v>13</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>11.9</v>
+      </c>
       <c r="L21" s="2" t="s">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="13" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>205</v>
+        <v>132</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>47</v>
+        <v>203</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>46510</v>
-      </c>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-      <c r="X21" s="9"/>
-      <c r="Y21" s="10" t="s">
-        <v>299</v>
+        <v>46331</v>
+      </c>
+      <c r="V21" s="5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X21" s="5" t="n">
+        <v>750000</v>
+      </c>
+      <c r="Y21" s="9"/>
+      <c r="Z21" s="10" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E22" s="13" t="n">
         <v>10</v>
@@ -5190,22 +5441,22 @@
         <v>10584340</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H22" s="13" t="n">
         <v>13</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>10.6</v>
+        <v>11.3</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>1</v>
@@ -5214,49 +5465,52 @@
         <v>6.7</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>199</v>
+        <v>48</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>47052</v>
+        <v>46455</v>
       </c>
       <c r="V22" s="5" t="n">
-        <v>550000</v>
-      </c>
-      <c r="W22" s="5" t="n">
-        <v>50000</v>
-      </c>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="10" t="s">
-        <v>304</v>
+        <v>900000</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X22" s="5" t="n">
+        <v>450000</v>
+      </c>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="10" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>10</v>
@@ -5265,22 +5519,22 @@
         <v>10584340</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H23" s="13" t="n">
         <v>13</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="K23" s="13" t="n">
-        <v>6.9</v>
+        <v>8.4</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>1</v>
@@ -5289,105 +5543,121 @@
         <v>6.7</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>237</v>
+        <v>132</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>47</v>
+        <v>203</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>46510</v>
+        <v>47052</v>
       </c>
       <c r="V23" s="5" t="n">
-        <v>450000</v>
-      </c>
-      <c r="W23" s="5" t="n">
-        <v>450000</v>
-      </c>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="10" t="s">
-        <v>309</v>
+        <v>550000</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X23" s="5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="10" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>1402172</v>
+        <v>10584340</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I24" s="12"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
+        <v>13</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J24" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>5.3</v>
+      </c>
       <c r="L24" s="2" t="s">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="13" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>55</v>
+        <v>266</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>46461</v>
-      </c>
-      <c r="V24" s="5"/>
-      <c r="W24" s="5"/>
-      <c r="X24" s="9"/>
-      <c r="Y24" s="10" t="s">
-        <v>314</v>
+        <v>46510</v>
+      </c>
+      <c r="V24" s="5" t="n">
+        <v>450000</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X24" s="5" t="n">
+        <v>450000</v>
+      </c>
+      <c r="Y24" s="9"/>
+      <c r="Z24" s="10" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>24</v>
@@ -5396,7 +5666,7 @@
         <v>29</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>16.7</v>
@@ -5405,7 +5675,7 @@
         <v>618846</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H25" s="13" t="n">
         <v>1.7</v>
@@ -5414,7 +5684,7 @@
       <c r="J25" s="13"/>
       <c r="K25" s="13"/>
       <c r="L25" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>1</v>
@@ -5423,58 +5693,61 @@
         <v>11.1</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U25" s="4"/>
       <c r="V25" s="5"/>
-      <c r="W25" s="5"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="10" t="s">
-        <v>321</v>
+      <c r="W25" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="X25" s="5"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="10" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y25"/>
+  <autoFilter ref="A1:Z25"/>
   <hyperlinks>
-    <hyperlink ref="Y2" r:id="rId1h"/>
-    <hyperlink ref="Y3" r:id="rId2h"/>
-    <hyperlink ref="Y4" r:id="rId3h"/>
-    <hyperlink ref="Y5" r:id="rId4h"/>
-    <hyperlink ref="Y6" r:id="rId5h"/>
-    <hyperlink ref="Y7" r:id="rId6h"/>
-    <hyperlink ref="Y8" r:id="rId7h"/>
-    <hyperlink ref="Y9" r:id="rId8h"/>
-    <hyperlink ref="Y10" r:id="rId9h"/>
-    <hyperlink ref="Y11" r:id="rId10h"/>
-    <hyperlink ref="Y12" r:id="rId11h"/>
-    <hyperlink ref="Y13" r:id="rId12h"/>
-    <hyperlink ref="Y14" r:id="rId13h"/>
-    <hyperlink ref="Y15" r:id="rId14h"/>
-    <hyperlink ref="Y16" r:id="rId15h"/>
-    <hyperlink ref="Y17" r:id="rId16h"/>
-    <hyperlink ref="Y18" r:id="rId17h"/>
-    <hyperlink ref="Y19" r:id="rId18h"/>
-    <hyperlink ref="Y20" r:id="rId19h"/>
-    <hyperlink ref="Y21" r:id="rId20h"/>
-    <hyperlink ref="Y22" r:id="rId21h"/>
-    <hyperlink ref="Y23" r:id="rId22h"/>
-    <hyperlink ref="Y24" r:id="rId23h"/>
-    <hyperlink ref="Y25" r:id="rId24h"/>
+    <hyperlink ref="Z2" r:id="rId1h"/>
+    <hyperlink ref="Z3" r:id="rId2h"/>
+    <hyperlink ref="Z4" r:id="rId3h"/>
+    <hyperlink ref="Z5" r:id="rId4h"/>
+    <hyperlink ref="Z6" r:id="rId5h"/>
+    <hyperlink ref="Z7" r:id="rId6h"/>
+    <hyperlink ref="Z8" r:id="rId7h"/>
+    <hyperlink ref="Z9" r:id="rId8h"/>
+    <hyperlink ref="Z10" r:id="rId9h"/>
+    <hyperlink ref="Z11" r:id="rId10h"/>
+    <hyperlink ref="Z12" r:id="rId11h"/>
+    <hyperlink ref="Z13" r:id="rId12h"/>
+    <hyperlink ref="Z14" r:id="rId13h"/>
+    <hyperlink ref="Z15" r:id="rId14h"/>
+    <hyperlink ref="Z16" r:id="rId15h"/>
+    <hyperlink ref="Z17" r:id="rId16h"/>
+    <hyperlink ref="Z18" r:id="rId17h"/>
+    <hyperlink ref="Z19" r:id="rId18h"/>
+    <hyperlink ref="Z20" r:id="rId19h"/>
+    <hyperlink ref="Z21" r:id="rId20h"/>
+    <hyperlink ref="Z22" r:id="rId21h"/>
+    <hyperlink ref="Z23" r:id="rId22h"/>
+    <hyperlink ref="Z24" r:id="rId23h"/>
+    <hyperlink ref="Z25" r:id="rId24h"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -5508,9 +5781,10 @@
     <col min="20" max="20" width="11.71" hidden="0" customWidth="1"/>
     <col min="21" max="21" width="13.71" hidden="0" customWidth="1"/>
     <col min="22" max="22" width="14.71" hidden="0" customWidth="1"/>
-    <col min="23" max="23" width="13.71" hidden="0" customWidth="1"/>
-    <col min="24" max="24" width="55.71" hidden="0" customWidth="1"/>
-    <col min="25" max="25" width="30.71" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="24.71" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="13.71" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="55.71" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="30.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5589,10 +5863,13 @@
       <c r="Y1" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="Z1" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -5601,7 +5878,7 @@
         <v>73</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E2" s="16" t="n">
         <v>20</v>
@@ -5610,7 +5887,7 @@
         <v>10584340</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2" s="16" t="n">
         <v>13</v>
@@ -5625,7 +5902,7 @@
         <v>19</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>1</v>
@@ -5634,22 +5911,22 @@
         <v>6.7</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>46346</v>
@@ -5657,17 +5934,20 @@
       <c r="V2" s="5" t="n">
         <v>15000000</v>
       </c>
-      <c r="W2" s="5" t="n">
+      <c r="W2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X2" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="10" t="s">
-        <v>327</v>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="10" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -5676,7 +5956,7 @@
         <v>67</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E3" s="16" t="n">
         <v>20</v>
@@ -5685,7 +5965,7 @@
         <v>127227</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="H3" s="16" t="n">
         <v>0.3</v>
@@ -5700,7 +5980,7 @@
         <v>19.9</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>1</v>
@@ -5709,22 +5989,22 @@
         <v>6.7</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U3" s="4" t="n">
         <v>46464</v>
@@ -5732,17 +6012,20 @@
       <c r="V3" s="5" t="n">
         <v>48596938</v>
       </c>
-      <c r="W3" s="5" t="n">
+      <c r="W3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X3" s="5" t="n">
         <v>3285203</v>
       </c>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="10" t="s">
-        <v>332</v>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="10" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
@@ -5751,7 +6034,7 @@
         <v>65</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E4" s="16" t="n">
         <v>10</v>
@@ -5760,7 +6043,7 @@
         <v>10584340</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H4" s="16" t="n">
         <v>13</v>
@@ -5769,13 +6052,13 @@
         <v>2.08</v>
       </c>
       <c r="J4" s="16" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>1</v>
@@ -5784,22 +6067,22 @@
         <v>6.7</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>46398</v>
@@ -5807,17 +6090,20 @@
       <c r="V4" s="5" t="n">
         <v>22000000</v>
       </c>
-      <c r="W4" s="5" t="n">
+      <c r="W4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X4" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="10" t="s">
-        <v>338</v>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="10" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -5826,7 +6112,7 @@
         <v>77</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E5" s="16" t="n">
         <v>20</v>
@@ -5835,7 +6121,7 @@
         <v>618846</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H5" s="16" t="n">
         <v>10</v>
@@ -5850,7 +6136,7 @@
         <v>20</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>1</v>
@@ -5859,38 +6145,41 @@
         <v>6.7</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="5" t="n">
         <v>275000000</v>
       </c>
-      <c r="W5" s="5" t="n">
+      <c r="W5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X5" s="5" t="n">
         <v>260000</v>
       </c>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="10" t="s">
-        <v>346</v>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="10" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
@@ -5899,7 +6188,7 @@
         <v>61</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E6" s="16" t="n">
         <v>33.3</v>
@@ -5908,7 +6197,7 @@
         <v>618846</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H6" s="16" t="n">
         <v>16.7</v>
@@ -5917,7 +6206,7 @@
       <c r="J6" s="16"/>
       <c r="K6" s="16"/>
       <c r="L6" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>1</v>
@@ -5926,34 +6215,37 @@
         <v>11.1</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="10" t="s">
-        <v>321</v>
+      <c r="W6" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="10" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>3</v>
@@ -5962,7 +6254,7 @@
         <v>37</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E7" s="16" t="n">
         <v>20</v>
@@ -5971,7 +6263,7 @@
         <v>618846</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H7" s="16" t="n">
         <v>10</v>
@@ -5986,7 +6278,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>1</v>
@@ -5995,22 +6287,22 @@
         <v>6.7</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>46486</v>
@@ -6018,23 +6310,26 @@
       <c r="V7" s="5" t="n">
         <v>400000</v>
       </c>
-      <c r="W7" s="5" t="n">
+      <c r="W7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X7" s="5" t="n">
         <v>50000</v>
       </c>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="10" t="s">
-        <v>352</v>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="10" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y7"/>
+  <autoFilter ref="A1:Z7"/>
   <hyperlinks>
-    <hyperlink ref="Y2" r:id="rId1h"/>
-    <hyperlink ref="Y3" r:id="rId2h"/>
-    <hyperlink ref="Y4" r:id="rId3h"/>
-    <hyperlink ref="Y5" r:id="rId4h"/>
-    <hyperlink ref="Y6" r:id="rId5h"/>
-    <hyperlink ref="Y7" r:id="rId6h"/>
+    <hyperlink ref="Z2" r:id="rId1h"/>
+    <hyperlink ref="Z3" r:id="rId2h"/>
+    <hyperlink ref="Z4" r:id="rId3h"/>
+    <hyperlink ref="Z5" r:id="rId4h"/>
+    <hyperlink ref="Z6" r:id="rId5h"/>
+    <hyperlink ref="Z7" r:id="rId6h"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
